--- a/test/原料数据库导入_完整版_已清理.xlsx
+++ b/test/原料数据库导入_完整版_已清理.xlsx
@@ -1,46 +1,704 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program Data\workspace-codebd\TingStudio\test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0AC674-5D6B-406F-AC99-7E810D492DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="原料数据" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">原料数据!$A$1:$S$64</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="219">
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>原料名称</t>
+  </si>
+  <si>
+    <t>编码</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>库存</t>
+  </si>
+  <si>
+    <t>蛋白质(g/100g)</t>
+  </si>
+  <si>
+    <t>脂肪(g/100g)</t>
+  </si>
+  <si>
+    <t>碳水化合物(g/100g)</t>
+  </si>
+  <si>
+    <t>钠(mg/100g)</t>
+  </si>
+  <si>
+    <t>数据来源</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>蛋白质</t>
+  </si>
+  <si>
+    <t>脂肪</t>
+  </si>
+  <si>
+    <t>碳水化合物</t>
+  </si>
+  <si>
+    <t>钠</t>
+  </si>
+  <si>
+    <t>unit_price（元/kg）</t>
+  </si>
+  <si>
+    <t>96bd8cf8...</t>
+  </si>
+  <si>
+    <t>阿胶</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>辅料</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>酸枣仁灵芝石斛膏</t>
+  </si>
+  <si>
+    <t>2026-04-25T01:19:54</t>
+  </si>
+  <si>
+    <t>ac709b00...</t>
+  </si>
+  <si>
+    <t>白芷</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>药材</t>
+  </si>
+  <si>
+    <t>正阳御湿膏</t>
+  </si>
+  <si>
+    <t>cd9eb810...</t>
+  </si>
+  <si>
+    <t>百合</t>
+  </si>
+  <si>
+    <t>BH</t>
+  </si>
+  <si>
+    <t>08dd2ce9...</t>
+  </si>
+  <si>
+    <t>草果</t>
+  </si>
+  <si>
+    <t>RE</t>
+  </si>
+  <si>
+    <t>521ee0de...</t>
+  </si>
+  <si>
+    <t>炒白扁豆</t>
+  </si>
+  <si>
+    <t>KRLE</t>
+  </si>
+  <si>
+    <t>29677d26...</t>
+  </si>
+  <si>
+    <t>陈皮</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>e20241e0...</t>
+  </si>
+  <si>
+    <t>大枣</t>
+  </si>
+  <si>
+    <t>VL</t>
+  </si>
+  <si>
+    <t>c88e1a3c...</t>
+  </si>
+  <si>
+    <t>当归</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>沫彐淳膏</t>
+  </si>
+  <si>
+    <t>b4e8558a...</t>
+  </si>
+  <si>
+    <t>党参</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>946c6533...</t>
+  </si>
+  <si>
+    <t>地龙蛋白肽粉</t>
+  </si>
+  <si>
+    <t>MLFR</t>
+  </si>
+  <si>
+    <t>40bb9619...</t>
+  </si>
+  <si>
+    <t>低聚异麦芽糖</t>
+  </si>
+  <si>
+    <t>WUMC</t>
+  </si>
+  <si>
+    <t>3d7116e5...</t>
+  </si>
+  <si>
+    <t>短梗五加</t>
+  </si>
+  <si>
+    <t>VVSO</t>
+  </si>
+  <si>
+    <t>dbf13746...</t>
+  </si>
+  <si>
+    <t>佛手</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>佛手玫苓膏</t>
+  </si>
+  <si>
+    <t>2877e108...</t>
+  </si>
+  <si>
+    <t>茯苓</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>cbd63f05...</t>
+  </si>
+  <si>
+    <t>甘草</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>b05ac750...</t>
+  </si>
+  <si>
+    <t>葛根</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>6b539b44...</t>
+  </si>
+  <si>
+    <t>枸杞子</t>
+  </si>
+  <si>
+    <t>GUC</t>
+  </si>
+  <si>
+    <t>12fe1a90...</t>
+  </si>
+  <si>
+    <t>荷叶</t>
+  </si>
+  <si>
+    <t>LS</t>
+  </si>
+  <si>
+    <t>8e7fa4e2...</t>
+  </si>
+  <si>
+    <t>黄精</t>
+  </si>
+  <si>
+    <t>HJ</t>
+  </si>
+  <si>
+    <t>dbc6f873...</t>
+  </si>
+  <si>
+    <t>黄芪</t>
+  </si>
+  <si>
+    <t>HQ</t>
+  </si>
+  <si>
+    <t>9b09c850...</t>
+  </si>
+  <si>
+    <t>藿香</t>
+  </si>
+  <si>
+    <t>JJ</t>
+  </si>
+  <si>
+    <t>刘明膏滋营养成分表20260303</t>
+  </si>
+  <si>
+    <t>8d74d2ea...</t>
+  </si>
+  <si>
+    <t>桔梗</t>
+  </si>
+  <si>
+    <t>GV</t>
+  </si>
+  <si>
+    <t>1c92892a...</t>
+  </si>
+  <si>
+    <t>金银花</t>
+  </si>
+  <si>
+    <t>JYH</t>
+  </si>
+  <si>
+    <t>9f853c45...</t>
+  </si>
+  <si>
+    <t>莲子</t>
+  </si>
+  <si>
+    <t>LZ</t>
+  </si>
+  <si>
+    <t>1802738b...</t>
+  </si>
+  <si>
+    <t>灵芝</t>
+  </si>
+  <si>
+    <t>f7218cdd...</t>
+  </si>
+  <si>
+    <t>纳豆</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>6f3758ef...</t>
+  </si>
+  <si>
+    <t>平卧菊三七</t>
+  </si>
+  <si>
+    <t>ZFQJ</t>
+  </si>
+  <si>
+    <t>f7f08752...</t>
+  </si>
+  <si>
+    <t>芡实</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>047479ad...</t>
+  </si>
+  <si>
+    <t>肉豆蔻</t>
+  </si>
+  <si>
+    <t>PEV</t>
+  </si>
+  <si>
+    <t>8fb861f0...</t>
+  </si>
+  <si>
+    <t>肉桂</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>b051002a...</t>
+  </si>
+  <si>
+    <t>桑椹</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>19f2c241...</t>
+  </si>
+  <si>
+    <t>沙棘</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>c27dea5f...</t>
+  </si>
+  <si>
+    <t>山药</t>
+  </si>
+  <si>
+    <t>SY</t>
+  </si>
+  <si>
+    <t>a80c55a9...</t>
+  </si>
+  <si>
+    <t>酸枣仁</t>
+  </si>
+  <si>
+    <t>SZR</t>
+  </si>
+  <si>
+    <t>a8261cbb...</t>
+  </si>
+  <si>
+    <t>桃仁</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>a07636cf...</t>
+  </si>
+  <si>
+    <t>铁皮石斛</t>
+  </si>
+  <si>
+    <t>ROBL</t>
+  </si>
+  <si>
+    <t>808270c3...</t>
+  </si>
+  <si>
+    <t>乌梅</t>
+  </si>
+  <si>
+    <t>YD</t>
+  </si>
+  <si>
+    <t>4a2b1762...</t>
+  </si>
+  <si>
+    <t>西红花</t>
+  </si>
+  <si>
+    <t>VWV</t>
+  </si>
+  <si>
+    <t>d8d832ac...</t>
+  </si>
+  <si>
+    <t>显脉旋覆花</t>
+  </si>
+  <si>
+    <t>SNHC</t>
+  </si>
+  <si>
+    <t>1ebed193...</t>
+  </si>
+  <si>
+    <t>香橼</t>
+  </si>
+  <si>
+    <t>JM</t>
+  </si>
+  <si>
+    <t>f02f892b...</t>
+  </si>
+  <si>
+    <t>小茴香</t>
+  </si>
+  <si>
+    <t>LWJ</t>
+  </si>
+  <si>
+    <t>0955b393...</t>
+  </si>
+  <si>
+    <t>小麦</t>
+  </si>
+  <si>
+    <t>LC</t>
+  </si>
+  <si>
+    <t>7af62f84...</t>
+  </si>
+  <si>
+    <t>栀子</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>cf6a560c...</t>
+  </si>
+  <si>
+    <t>重瓣红玫瑰</t>
+  </si>
+  <si>
+    <t>PXWX</t>
+  </si>
+  <si>
+    <t>84dc838a...</t>
+  </si>
+  <si>
+    <t>重瓣玫瑰花</t>
+  </si>
+  <si>
+    <t>PXXM</t>
+  </si>
+  <si>
+    <t>15acc31e48bd017035fc30f4</t>
+  </si>
+  <si>
+    <t>淡竹叶</t>
+  </si>
+  <si>
+    <t>DZY</t>
+  </si>
+  <si>
+    <t>原料</t>
+  </si>
+  <si>
+    <t>2026-04-25 04:27:25</t>
+  </si>
+  <si>
+    <t>7b95282de34daf3b3a5ce3c6</t>
+  </si>
+  <si>
+    <t>槐花</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>facb99f9c8f41399941bb499</t>
+  </si>
+  <si>
+    <t>马齿苋</t>
+  </si>
+  <si>
+    <t>MCX</t>
+  </si>
+  <si>
+    <t>5a4389b30d8fda3c09180882</t>
+  </si>
+  <si>
+    <t>薏苡仁</t>
+  </si>
+  <si>
+    <t>YYR</t>
+  </si>
+  <si>
+    <t>1eb648aad7da3913bdf223cb</t>
+  </si>
+  <si>
+    <t>莱菔子</t>
+  </si>
+  <si>
+    <t>LFZ</t>
+  </si>
+  <si>
+    <t>e1c4bd9437d549325317d99a</t>
+  </si>
+  <si>
+    <t>山楂</t>
+  </si>
+  <si>
+    <t>SZ</t>
+  </si>
+  <si>
+    <t>110ae8b9091d24dc7c127214</t>
+  </si>
+  <si>
+    <t>麦芽</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>78e72df182152ba6989ebf44</t>
+  </si>
+  <si>
+    <t>杏仁</t>
+  </si>
+  <si>
+    <t>XR</t>
+  </si>
+  <si>
+    <t>e9a993eab42b596bec2f1605</t>
+  </si>
+  <si>
+    <t>火麻仁</t>
+  </si>
+  <si>
+    <t>HMR</t>
+  </si>
+  <si>
+    <t>e78e9bea50577e3e826b320c</t>
+  </si>
+  <si>
+    <t>鱼腥草</t>
+  </si>
+  <si>
+    <t>YXC</t>
+  </si>
+  <si>
+    <t>08cb40e51c88a479b73ee8e0</t>
+  </si>
+  <si>
+    <t>赤小豆</t>
+  </si>
+  <si>
+    <t>CXD</t>
+  </si>
+  <si>
+    <t>MAT_dfd71344_225cc5</t>
+  </si>
+  <si>
+    <t>2026-04-25 02:55:21</t>
+  </si>
+  <si>
+    <t>MAT_e9eabdcd4eb047</t>
+  </si>
+  <si>
+    <t>桑葫鲜果</t>
+  </si>
+  <si>
+    <t>SSXG</t>
+  </si>
+  <si>
+    <t>2026-04-25T23:53:31.421Z</t>
+  </si>
+  <si>
+    <t>MAT_72387001c4964d</t>
+  </si>
+  <si>
+    <t>酸枣蜜炼</t>
+  </si>
+  <si>
+    <t>SZML</t>
+  </si>
+  <si>
+    <t>MAT_b590e0058b6b4f</t>
+  </si>
+  <si>
+    <t>黄精蜜炼</t>
+  </si>
+  <si>
+    <t>HJML</t>
+  </si>
+  <si>
+    <t>MAT_11db658a0c8f49</t>
+  </si>
+  <si>
+    <t>薄荷</t>
+  </si>
+  <si>
+    <t>BH2</t>
+  </si>
+  <si>
+    <t>MAT_765a53ebb2784e</t>
+  </si>
+  <si>
+    <t>麦冬</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>MAT_e6d32d4c4e134f</t>
+  </si>
+  <si>
+    <t>白术</t>
+  </si>
+  <si>
+    <t>BS2</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,13 +723,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,83 +1062,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S64"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" customWidth="1"/>
+    <col min="2" max="2" width="20.796875" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" customWidth="1"/>
+    <col min="5" max="5" width="8.796875" customWidth="1"/>
+    <col min="6" max="6" width="6.796875" customWidth="1"/>
+    <col min="7" max="7" width="8.796875" customWidth="1"/>
+    <col min="8" max="8" width="15.796875" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" customWidth="1"/>
+    <col min="10" max="10" width="14.796875" customWidth="1"/>
+    <col min="11" max="11" width="12.796875" customWidth="1"/>
+    <col min="12" max="12" width="20.796875" customWidth="1"/>
+    <col min="13" max="13" width="18.796875" customWidth="1"/>
+    <col min="14" max="14" width="8.796875" customWidth="1"/>
+    <col min="15" max="15" width="18.796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>原料名称</v>
-      </c>
-      <c r="D1" t="str">
-        <v>编码</v>
-      </c>
-      <c r="E1" t="str">
-        <v>类型</v>
-      </c>
-      <c r="F1" t="str">
-        <v>单位</v>
-      </c>
-      <c r="G1" t="str">
-        <v>库存</v>
-      </c>
-      <c r="H1" t="str">
-        <v>蛋白质(g/100g)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>脂肪(g/100g)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>碳水化合物(g/100g)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>钠(mg/100g)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>数据来源</v>
-      </c>
-      <c r="M1" t="str">
-        <v>创建时间</v>
-      </c>
-      <c r="N1" t="str">
-        <v>分类</v>
-      </c>
-      <c r="O1" t="str">
-        <v>蛋白质</v>
-      </c>
-      <c r="P1" t="str">
-        <v>脂肪</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>碳水化合物</v>
-      </c>
-      <c r="R1" t="str">
-        <v>钠</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>96bd8cf8...</v>
-      </c>
-      <c r="C2" t="str">
-        <v>阿胶</v>
-      </c>
-      <c r="D2" t="str">
-        <v>EJ</v>
-      </c>
-      <c r="E2" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F2" t="str">
-        <v>g</v>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -486,17 +1173,17 @@
       <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N2" t="str">
-        <v>辅料</v>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
       <c r="O2">
         <v>80</v>
@@ -510,25 +1197,28 @@
       <c r="R2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="S2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>ac709b00...</v>
-      </c>
-      <c r="C3" t="str">
-        <v>白芷</v>
-      </c>
-      <c r="D3" t="str">
-        <v>RB</v>
-      </c>
-      <c r="E3" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F3" t="str">
-        <v>g</v>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -540,19 +1230,19 @@
         <v>1.5</v>
       </c>
       <c r="J3">
-        <v>74.1</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="K3">
         <v>27</v>
       </c>
-      <c r="L3" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N3" t="str">
-        <v>药材</v>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
       </c>
       <c r="O3">
         <v>8.9</v>
@@ -561,30 +1251,33 @@
         <v>1.5</v>
       </c>
       <c r="Q3">
-        <v>74.1</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="R3">
         <v>75</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="S3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>cd9eb810...</v>
-      </c>
-      <c r="C4" t="str">
-        <v>百合</v>
-      </c>
-      <c r="D4" t="str">
-        <v>BH</v>
-      </c>
-      <c r="E4" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F4" t="str">
-        <v>g</v>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -601,14 +1294,14 @@
       <c r="K4">
         <v>37</v>
       </c>
-      <c r="L4" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N4" t="str">
-        <v>药材</v>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
       </c>
       <c r="O4">
         <v>6.7</v>
@@ -622,25 +1315,28 @@
       <c r="R4">
         <v>48</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="S4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>08dd2ce9...</v>
-      </c>
-      <c r="C5" t="str">
-        <v>草果</v>
-      </c>
-      <c r="D5" t="str">
-        <v>RE</v>
-      </c>
-      <c r="E5" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F5" t="str">
-        <v>g</v>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -657,14 +1353,14 @@
       <c r="K5">
         <v>5</v>
       </c>
-      <c r="L5" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N5" t="str">
-        <v>药材</v>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
       </c>
       <c r="O5">
         <v>2.9</v>
@@ -678,25 +1374,28 @@
       <c r="R5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="S5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>521ee0de...</v>
-      </c>
-      <c r="C6" t="str">
-        <v>炒白扁豆</v>
-      </c>
-      <c r="D6" t="str">
-        <v>KRLE</v>
-      </c>
-      <c r="E6" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F6" t="str">
-        <v>g</v>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -710,17 +1409,17 @@
       <c r="J6">
         <v>55.6</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M6" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N6" t="str">
-        <v>药材</v>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
       </c>
       <c r="O6">
         <v>19</v>
@@ -734,25 +1433,28 @@
       <c r="R6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>29677d26...</v>
-      </c>
-      <c r="C7" t="str">
-        <v>陈皮</v>
-      </c>
-      <c r="D7" t="str">
-        <v>CP</v>
-      </c>
-      <c r="E7" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F7" t="str">
-        <v>g</v>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -769,14 +1471,14 @@
       <c r="K7">
         <v>21</v>
       </c>
-      <c r="L7" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M7" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N7" t="str">
-        <v>药材</v>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
       </c>
       <c r="O7">
         <v>8</v>
@@ -790,25 +1492,28 @@
       <c r="R7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="S7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>e20241e0...</v>
-      </c>
-      <c r="C8" t="str">
-        <v>大枣</v>
-      </c>
-      <c r="D8" t="str">
-        <v>VL</v>
-      </c>
-      <c r="E8" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F8" t="str">
-        <v>g</v>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -825,14 +1530,14 @@
       <c r="K8">
         <v>6</v>
       </c>
-      <c r="L8" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M8" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N8" t="str">
-        <v>药材</v>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>30</v>
       </c>
       <c r="O8">
         <v>3.2</v>
@@ -846,25 +1551,28 @@
       <c r="R8">
         <v>70</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="S8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>c88e1a3c...</v>
-      </c>
-      <c r="C9" t="str">
-        <v>当归</v>
-      </c>
-      <c r="D9" t="str">
-        <v>DG</v>
-      </c>
-      <c r="E9" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F9" t="str">
-        <v>g</v>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -878,17 +1586,17 @@
       <c r="J9">
         <v>18.2</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M9" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N9" t="str">
-        <v>药材</v>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
       </c>
       <c r="O9">
         <v>44.2</v>
@@ -902,25 +1610,28 @@
       <c r="R9">
         <v>130</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="S9">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>b4e8558a...</v>
-      </c>
-      <c r="C10" t="str">
-        <v>党参</v>
-      </c>
-      <c r="D10" t="str">
-        <v>DS</v>
-      </c>
-      <c r="E10" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F10" t="str">
-        <v>g</v>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -934,17 +1645,17 @@
       <c r="J10">
         <v>10.4</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M10" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N10" t="str">
-        <v>药材</v>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
       </c>
       <c r="O10">
         <v>53.7</v>
@@ -958,25 +1669,28 @@
       <c r="R10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="S10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>946c6533...</v>
-      </c>
-      <c r="C11" t="str">
-        <v>地龙蛋白肽粉</v>
-      </c>
-      <c r="D11" t="str">
-        <v>MLFR</v>
-      </c>
-      <c r="E11" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F11" t="str">
-        <v>g</v>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -990,17 +1704,17 @@
       <c r="J11">
         <v>15</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M11" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N11" t="str">
-        <v>辅料</v>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
       </c>
       <c r="O11">
         <v>60</v>
@@ -1014,49 +1728,52 @@
       <c r="R11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="S11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>40bb9619...</v>
-      </c>
-      <c r="C12" t="str">
-        <v>低聚异麦芽糖</v>
-      </c>
-      <c r="D12" t="str">
-        <v>WUMC</v>
-      </c>
-      <c r="E12" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F12" t="str">
-        <v>g</v>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>24</v>
       </c>
       <c r="J12">
         <v>90</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M12" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N12" t="str">
-        <v>辅料</v>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>22</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1070,25 +1787,28 @@
       <c r="R12">
         <v>10.8</v>
       </c>
-    </row>
-    <row r="13">
+      <c r="S12">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>3d7116e5...</v>
-      </c>
-      <c r="C13" t="str">
-        <v>短梗五加</v>
-      </c>
-      <c r="D13" t="str">
-        <v>VVSO</v>
-      </c>
-      <c r="E13" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F13" t="str">
-        <v>g</v>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1096,23 +1816,23 @@
       <c r="H13">
         <v>12</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
+      <c r="I13" t="s">
+        <v>24</v>
       </c>
       <c r="J13">
         <v>65</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M13" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N13" t="str">
-        <v>药材</v>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
       </c>
       <c r="O13">
         <v>12</v>
@@ -1126,25 +1846,28 @@
       <c r="R13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="S13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>dbf13746...</v>
-      </c>
-      <c r="C14" t="str">
-        <v>佛手</v>
-      </c>
-      <c r="D14" t="str">
-        <v>FS</v>
-      </c>
-      <c r="E14" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F14" t="str">
-        <v>g</v>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>23</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1158,17 +1881,17 @@
       <c r="J14">
         <v>92</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>佛手玫苓膏</v>
-      </c>
-      <c r="M14" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N14" t="str">
-        <v>药材</v>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
       </c>
       <c r="O14">
         <v>1.2</v>
@@ -1182,25 +1905,28 @@
       <c r="R14">
         <v>60</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="S14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
-      <c r="B15" t="str">
-        <v>2877e108...</v>
-      </c>
-      <c r="C15" t="str">
-        <v>茯苓</v>
-      </c>
-      <c r="D15" t="str">
-        <v>FL</v>
-      </c>
-      <c r="E15" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F15" t="str">
-        <v>g</v>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1217,14 +1943,14 @@
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="L15" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M15" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N15" t="str">
-        <v>药材</v>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" t="s">
+        <v>30</v>
       </c>
       <c r="O15">
         <v>1.2</v>
@@ -1238,31 +1964,34 @@
       <c r="R15">
         <v>35</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="S15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
-      <c r="B16" t="str">
-        <v>cbd63f05...</v>
-      </c>
-      <c r="C16" t="str">
-        <v>甘草</v>
-      </c>
-      <c r="D16" t="str">
-        <v>GC</v>
-      </c>
-      <c r="E16" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F16" t="str">
-        <v>g</v>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I16">
         <v>4.2</v>
@@ -1273,17 +2002,17 @@
       <c r="K16">
         <v>155</v>
       </c>
-      <c r="L16" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M16" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N16" t="str">
-        <v>药材</v>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" t="s">
+        <v>30</v>
       </c>
       <c r="O16">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="P16">
         <v>4.2</v>
@@ -1294,25 +2023,28 @@
       <c r="R16">
         <v>40</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="S16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
-      <c r="B17" t="str">
-        <v>b05ac750...</v>
-      </c>
-      <c r="C17" t="str">
-        <v>葛根</v>
-      </c>
-      <c r="D17" t="str">
-        <v>FF</v>
-      </c>
-      <c r="E17" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F17" t="str">
-        <v>g</v>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1329,14 +2061,14 @@
       <c r="K17">
         <v>5</v>
       </c>
-      <c r="L17" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M17" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N17" t="str">
-        <v>药材</v>
+      <c r="L17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" t="s">
+        <v>30</v>
       </c>
       <c r="O17">
         <v>0.4</v>
@@ -1350,25 +2082,28 @@
       <c r="R17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18">
+      <c r="S17">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
-      <c r="B18" t="str">
-        <v>6b539b44...</v>
-      </c>
-      <c r="C18" t="str">
-        <v>枸杞子</v>
-      </c>
-      <c r="D18" t="str">
-        <v>GUC</v>
-      </c>
-      <c r="E18" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F18" t="str">
-        <v>g</v>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1380,19 +2115,19 @@
         <v>1.5</v>
       </c>
       <c r="J18">
-        <v>64.1</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="K18">
         <v>252</v>
       </c>
-      <c r="L18" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M18" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N18" t="str">
-        <v>药材</v>
+      <c r="L18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
       </c>
       <c r="O18">
         <v>13.9</v>
@@ -1401,30 +2136,33 @@
         <v>1.5</v>
       </c>
       <c r="Q18">
-        <v>64.1</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="R18">
         <v>252</v>
       </c>
-    </row>
-    <row r="19">
+      <c r="S18">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19" t="str">
-        <v>12fe1a90...</v>
-      </c>
-      <c r="C19" t="str">
-        <v>荷叶</v>
-      </c>
-      <c r="D19" t="str">
-        <v>LS</v>
-      </c>
-      <c r="E19" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F19" t="str">
-        <v>g</v>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1441,14 +2179,14 @@
       <c r="K19">
         <v>5</v>
       </c>
-      <c r="L19" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M19" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N19" t="str">
-        <v>药材</v>
+      <c r="L19" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" t="s">
+        <v>30</v>
       </c>
       <c r="O19">
         <v>3.1</v>
@@ -1462,25 +2200,28 @@
       <c r="R19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20">
+      <c r="S19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
-      <c r="B20" t="str">
-        <v>8e7fa4e2...</v>
-      </c>
-      <c r="C20" t="str">
-        <v>黄精</v>
-      </c>
-      <c r="D20" t="str">
-        <v>HJ</v>
-      </c>
-      <c r="E20" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F20" t="str">
-        <v>g</v>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1494,17 +2235,17 @@
       <c r="J20">
         <v>52.3</v>
       </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M20" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N20" t="str">
-        <v>药材</v>
+      <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" t="s">
+        <v>30</v>
       </c>
       <c r="O20">
         <v>11.6</v>
@@ -1518,25 +2259,28 @@
       <c r="R20">
         <v>78</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="S20">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21" t="str">
-        <v>dbc6f873...</v>
-      </c>
-      <c r="C21" t="str">
-        <v>黄芪</v>
-      </c>
-      <c r="D21" t="str">
-        <v>HQ</v>
-      </c>
-      <c r="E21" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F21" t="str">
-        <v>g</v>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1545,28 +2289,28 @@
         <v>14.9</v>
       </c>
       <c r="I21">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J21">
         <v>33.4</v>
       </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M21" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N21" t="str">
-        <v>药材</v>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" t="s">
+        <v>30</v>
       </c>
       <c r="O21">
         <v>14.9</v>
       </c>
       <c r="P21">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="Q21">
         <v>33.4</v>
@@ -1574,25 +2318,28 @@
       <c r="R21">
         <v>33</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="S21">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
-      <c r="B22" t="str">
-        <v>9b09c850...</v>
-      </c>
-      <c r="C22" t="str">
-        <v>藿香</v>
-      </c>
-      <c r="D22" t="str">
-        <v>JJ</v>
-      </c>
-      <c r="E22" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F22" t="str">
-        <v>g</v>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1609,14 +2356,14 @@
       <c r="K22">
         <v>46</v>
       </c>
-      <c r="L22" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M22" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N22" t="str">
-        <v>药材</v>
+      <c r="L22" t="s">
+        <v>91</v>
+      </c>
+      <c r="M22" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" t="s">
+        <v>30</v>
       </c>
       <c r="O22">
         <v>10.5</v>
@@ -1630,25 +2377,28 @@
       <c r="R22">
         <v>46</v>
       </c>
-    </row>
-    <row r="23">
+      <c r="S22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23" t="str">
-        <v>8d74d2ea...</v>
-      </c>
-      <c r="C23" t="str">
-        <v>桔梗</v>
-      </c>
-      <c r="D23" t="str">
-        <v>GV</v>
-      </c>
-      <c r="E23" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F23" t="str">
-        <v>g</v>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>23</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1660,19 +2410,19 @@
         <v>0.9</v>
       </c>
       <c r="J23">
-        <v>74.6</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="K23">
         <v>12</v>
       </c>
-      <c r="L23" t="str">
-        <v>佛手玫苓膏</v>
-      </c>
-      <c r="M23" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N23" t="str">
-        <v>药材</v>
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
+        <v>30</v>
       </c>
       <c r="O23">
         <v>10.7</v>
@@ -1681,30 +2431,33 @@
         <v>0.9</v>
       </c>
       <c r="Q23">
-        <v>74.6</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="R23">
         <v>56</v>
       </c>
-    </row>
-    <row r="24">
+      <c r="S23">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>24</v>
       </c>
-      <c r="B24" t="str">
-        <v>1c92892a...</v>
-      </c>
-      <c r="C24" t="str">
-        <v>金银花</v>
-      </c>
-      <c r="D24" t="str">
-        <v>JYH</v>
-      </c>
-      <c r="E24" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F24" t="str">
-        <v>g</v>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1716,19 +2469,19 @@
         <v>4.5</v>
       </c>
       <c r="J24">
-        <v>32.8</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M24" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N24" t="str">
-        <v>药材</v>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" t="s">
+        <v>30</v>
       </c>
       <c r="O24">
         <v>13.1</v>
@@ -1737,30 +2490,33 @@
         <v>4.5</v>
       </c>
       <c r="Q24">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="R24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25">
+      <c r="S24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
-      <c r="B25" t="str">
-        <v>9f853c45...</v>
-      </c>
-      <c r="C25" t="str">
-        <v>莲子</v>
-      </c>
-      <c r="D25" t="str">
-        <v>LZ</v>
-      </c>
-      <c r="E25" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F25" t="str">
-        <v>g</v>
+      <c r="B25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1777,14 +2533,14 @@
       <c r="K25">
         <v>5</v>
       </c>
-      <c r="L25" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M25" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N25" t="str">
-        <v>药材</v>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" t="s">
+        <v>30</v>
       </c>
       <c r="O25">
         <v>17.2</v>
@@ -1798,25 +2554,28 @@
       <c r="R25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="S25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26</v>
       </c>
-      <c r="B26" t="str">
-        <v>1802738b...</v>
-      </c>
-      <c r="C26" t="str">
-        <v>灵芝</v>
-      </c>
-      <c r="D26" t="str">
-        <v>LZ</v>
-      </c>
-      <c r="E26" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F26" t="str">
-        <v>g</v>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1825,7 +2584,7 @@
         <v>88.8</v>
       </c>
       <c r="I26">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J26">
         <v>4.7</v>
@@ -1833,20 +2592,20 @@
       <c r="K26">
         <v>224</v>
       </c>
-      <c r="L26" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M26" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N26" t="str">
-        <v>药材</v>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" t="s">
+        <v>30</v>
       </c>
       <c r="O26">
         <v>88.8</v>
       </c>
       <c r="P26">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q26">
         <v>4.7</v>
@@ -1854,25 +2613,28 @@
       <c r="R26">
         <v>224</v>
       </c>
-    </row>
-    <row r="27">
+      <c r="S26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
-      <c r="B27" t="str">
-        <v>f7218cdd...</v>
-      </c>
-      <c r="C27" t="str">
-        <v>纳豆</v>
-      </c>
-      <c r="D27" t="str">
-        <v>NE</v>
-      </c>
-      <c r="E27" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F27" t="str">
-        <v>g</v>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>23</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1889,14 +2651,14 @@
       <c r="K27">
         <v>2</v>
       </c>
-      <c r="L27" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M27" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N27" t="str">
-        <v>药材</v>
+      <c r="L27" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" t="s">
+        <v>30</v>
       </c>
       <c r="O27">
         <v>20.2</v>
@@ -1910,25 +2672,28 @@
       <c r="R27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28">
+      <c r="S27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
-      <c r="B28" t="str">
-        <v>6f3758ef...</v>
-      </c>
-      <c r="C28" t="str">
-        <v>平卧菊三七</v>
-      </c>
-      <c r="D28" t="str">
-        <v>ZFQJ</v>
-      </c>
-      <c r="E28" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F28" t="str">
-        <v>g</v>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1940,19 +2705,19 @@
         <v>3.9</v>
       </c>
       <c r="J28">
-        <v>67.6</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="K28">
         <v>17.5</v>
       </c>
-      <c r="L28" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M28" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N28" t="str">
-        <v>药材</v>
+      <c r="L28" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" t="s">
+        <v>30</v>
       </c>
       <c r="O28">
         <v>6.8</v>
@@ -1961,86 +2726,92 @@
         <v>3.9</v>
       </c>
       <c r="Q28">
-        <v>67.6</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="R28">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="29">
+      <c r="S28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
-      <c r="B29" t="str">
-        <v>f7f08752...</v>
-      </c>
-      <c r="C29" t="str">
-        <v>芡实</v>
-      </c>
-      <c r="D29" t="str">
-        <v>QS</v>
-      </c>
-      <c r="E29" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F29" t="str">
-        <v>g</v>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I29">
         <v>0.3</v>
       </c>
       <c r="J29">
-        <v>79.6</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="K29">
         <v>28</v>
       </c>
-      <c r="L29" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M29" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N29" t="str">
-        <v>药材</v>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
+        <v>30</v>
       </c>
       <c r="O29">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="P29">
         <v>0.3</v>
       </c>
       <c r="Q29">
-        <v>79.6</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="R29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30">
+      <c r="S29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
-      <c r="B30" t="str">
-        <v>047479ad...</v>
-      </c>
-      <c r="C30" t="str">
-        <v>肉豆蔻</v>
-      </c>
-      <c r="D30" t="str">
-        <v>PEV</v>
-      </c>
-      <c r="E30" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F30" t="str">
-        <v>g</v>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -2049,7 +2820,7 @@
         <v>8.1</v>
       </c>
       <c r="I30">
-        <v>35.2</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="J30">
         <v>43.3</v>
@@ -2057,20 +2828,20 @@
       <c r="K30">
         <v>26</v>
       </c>
-      <c r="L30" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M30" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N30" t="str">
-        <v>药材</v>
+      <c r="L30" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" t="s">
+        <v>30</v>
       </c>
       <c r="O30">
         <v>8.1</v>
       </c>
       <c r="P30">
-        <v>35.2</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="Q30">
         <v>43.3</v>
@@ -2078,25 +2849,28 @@
       <c r="R30">
         <v>26</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="S30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
-      <c r="B31" t="str">
-        <v>8fb861f0...</v>
-      </c>
-      <c r="C31" t="str">
-        <v>肉桂</v>
-      </c>
-      <c r="D31" t="str">
-        <v>PO</v>
-      </c>
-      <c r="E31" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F31" t="str">
-        <v>g</v>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" t="s">
+        <v>23</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2113,14 +2887,14 @@
       <c r="K31">
         <v>15</v>
       </c>
-      <c r="L31" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M31" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N31" t="str">
-        <v>药材</v>
+      <c r="L31" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>30</v>
       </c>
       <c r="O31">
         <v>4</v>
@@ -2134,25 +2908,28 @@
       <c r="R31">
         <v>15</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="S31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
-      <c r="B32" t="str">
-        <v>b051002a...</v>
-      </c>
-      <c r="C32" t="str">
-        <v>桑椹</v>
-      </c>
-      <c r="D32" t="str">
-        <v>DB</v>
-      </c>
-      <c r="E32" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F32" t="str">
-        <v>g</v>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -2169,14 +2946,14 @@
       <c r="K32">
         <v>2</v>
       </c>
-      <c r="L32" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M32" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N32" t="str">
-        <v>药材</v>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
+        <v>30</v>
       </c>
       <c r="O32">
         <v>1.7</v>
@@ -2190,25 +2967,28 @@
       <c r="R32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="S32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
-      <c r="B33" t="str">
-        <v>19f2c241...</v>
-      </c>
-      <c r="C33" t="str">
-        <v>沙棘</v>
-      </c>
-      <c r="D33" t="str">
-        <v>HI</v>
-      </c>
-      <c r="E33" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F33" t="str">
-        <v>g</v>
+      <c r="B33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -2225,14 +3005,14 @@
       <c r="K33">
         <v>28</v>
       </c>
-      <c r="L33" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M33" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N33" t="str">
-        <v>药材</v>
+      <c r="L33" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>30</v>
       </c>
       <c r="O33">
         <v>0.9</v>
@@ -2246,25 +3026,28 @@
       <c r="R33">
         <v>28</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="S33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
-      <c r="B34" t="str">
-        <v>c27dea5f...</v>
-      </c>
-      <c r="C34" t="str">
-        <v>山药</v>
-      </c>
-      <c r="D34" t="str">
-        <v>SY</v>
-      </c>
-      <c r="E34" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F34" t="str">
-        <v>g</v>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2281,14 +3064,14 @@
       <c r="K34">
         <v>104</v>
       </c>
-      <c r="L34" t="str">
-        <v>佛手玫苓膏</v>
-      </c>
-      <c r="M34" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N34" t="str">
-        <v>药材</v>
+      <c r="L34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" t="s">
+        <v>30</v>
       </c>
       <c r="O34">
         <v>9.4</v>
@@ -2302,25 +3085,28 @@
       <c r="R34">
         <v>48</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="S34">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>37</v>
       </c>
-      <c r="B35" t="str">
-        <v>a80c55a9...</v>
-      </c>
-      <c r="C35" t="str">
-        <v>酸枣仁</v>
-      </c>
-      <c r="D35" t="str">
-        <v>SZR</v>
-      </c>
-      <c r="E35" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F35" t="str">
-        <v>g</v>
+      <c r="B35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" t="s">
+        <v>23</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2337,14 +3123,14 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="L35" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M35" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N35" t="str">
-        <v>药材</v>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" t="s">
+        <v>30</v>
       </c>
       <c r="O35">
         <v>31.8</v>
@@ -2358,25 +3144,28 @@
       <c r="R35">
         <v>380</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="S35">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>39</v>
       </c>
-      <c r="B36" t="str">
-        <v>a8261cbb...</v>
-      </c>
-      <c r="C36" t="str">
-        <v>桃仁</v>
-      </c>
-      <c r="D36" t="str">
-        <v>TR</v>
-      </c>
-      <c r="E36" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F36" t="str">
-        <v>g</v>
+      <c r="B36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" t="s">
+        <v>23</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -2388,19 +3177,19 @@
         <v>0.8</v>
       </c>
       <c r="J36">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="K36">
         <v>3.8</v>
       </c>
-      <c r="L36" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M36" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N36" t="str">
-        <v>药材</v>
+      <c r="L36" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>30</v>
       </c>
       <c r="O36">
         <v>7.4</v>
@@ -2409,30 +3198,33 @@
         <v>0.8</v>
       </c>
       <c r="Q36">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="R36">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="S36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
-      <c r="B37" t="str">
-        <v>a07636cf...</v>
-      </c>
-      <c r="C37" t="str">
-        <v>铁皮石斛</v>
-      </c>
-      <c r="D37" t="str">
-        <v>ROBL</v>
-      </c>
-      <c r="E37" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F37" t="str">
-        <v>g</v>
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" t="s">
+        <v>23</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -2446,17 +3238,17 @@
       <c r="J37">
         <v>9.5</v>
       </c>
-      <c r="K37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M37" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N37" t="str">
-        <v>药材</v>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>30</v>
       </c>
       <c r="O37">
         <v>1.6</v>
@@ -2470,25 +3262,28 @@
       <c r="R37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="S37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
-      <c r="B38" t="str">
-        <v>808270c3...</v>
-      </c>
-      <c r="C38" t="str">
-        <v>乌梅</v>
-      </c>
-      <c r="D38" t="str">
-        <v>YD</v>
-      </c>
-      <c r="E38" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F38" t="str">
-        <v>g</v>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" t="s">
+        <v>23</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -2497,54 +3292,57 @@
         <v>6.8</v>
       </c>
       <c r="I38">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J38">
-        <v>76.6</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="K38">
         <v>19</v>
       </c>
-      <c r="L38" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M38" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N38" t="str">
-        <v>药材</v>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>30</v>
       </c>
       <c r="O38">
         <v>6.8</v>
       </c>
       <c r="P38">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="Q38">
-        <v>76.6</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="R38">
         <v>70</v>
       </c>
-    </row>
-    <row r="39">
+      <c r="S38">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
-      <c r="B39" t="str">
-        <v>4a2b1762...</v>
-      </c>
-      <c r="C39" t="str">
-        <v>西红花</v>
-      </c>
-      <c r="D39" t="str">
-        <v>VWV</v>
-      </c>
-      <c r="E39" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F39" t="str">
-        <v>g</v>
+      <c r="B39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" t="s">
+        <v>23</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2556,19 +3354,19 @@
         <v>5.9</v>
       </c>
       <c r="J39">
-        <v>65.4</v>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M39" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N39" t="str">
-        <v>药材</v>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>30</v>
       </c>
       <c r="O39">
         <v>11.4</v>
@@ -2577,30 +3375,33 @@
         <v>5.9</v>
       </c>
       <c r="Q39">
-        <v>65.4</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="R39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40">
+      <c r="S39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
-      <c r="B40" t="str">
-        <v>d8d832ac...</v>
-      </c>
-      <c r="C40" t="str">
-        <v>显脉旋覆花</v>
-      </c>
-      <c r="D40" t="str">
-        <v>SNHC</v>
-      </c>
-      <c r="E40" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F40" t="str">
-        <v>g</v>
+      <c r="B40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" t="s">
+        <v>23</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -2614,17 +3415,17 @@
       <c r="J40">
         <v>62</v>
       </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
-      <c r="L40" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M40" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N40" t="str">
-        <v>药材</v>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" t="s">
+        <v>30</v>
       </c>
       <c r="O40">
         <v>5.5</v>
@@ -2638,25 +3439,28 @@
       <c r="R40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="S40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
-      <c r="B41" t="str">
-        <v>1ebed193...</v>
-      </c>
-      <c r="C41" t="str">
-        <v>香橼</v>
-      </c>
-      <c r="D41" t="str">
-        <v>JM</v>
-      </c>
-      <c r="E41" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F41" t="str">
-        <v>g</v>
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" t="s">
+        <v>147</v>
+      </c>
+      <c r="E41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2670,17 +3474,17 @@
       <c r="J41">
         <v>29.5</v>
       </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M41" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N41" t="str">
-        <v>药材</v>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>30</v>
       </c>
       <c r="O41">
         <v>6.9</v>
@@ -2694,25 +3498,28 @@
       <c r="R41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42">
+      <c r="S41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>46</v>
       </c>
-      <c r="B42" t="str">
-        <v>f02f892b...</v>
-      </c>
-      <c r="C42" t="str">
-        <v>小茴香</v>
-      </c>
-      <c r="D42" t="str">
-        <v>LWJ</v>
-      </c>
-      <c r="E42" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F42" t="str">
-        <v>g</v>
+      <c r="B42" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -2726,17 +3533,17 @@
       <c r="J42">
         <v>4.2</v>
       </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
-        <v>正阳御湿膏</v>
-      </c>
-      <c r="M42" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N42" t="str">
-        <v>药材</v>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>30</v>
       </c>
       <c r="O42">
         <v>2.5</v>
@@ -2750,25 +3557,28 @@
       <c r="R42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43">
+      <c r="S42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>47</v>
       </c>
-      <c r="B43" t="str">
-        <v>0955b393...</v>
-      </c>
-      <c r="C43" t="str">
-        <v>小麦</v>
-      </c>
-      <c r="D43" t="str">
-        <v>LC</v>
-      </c>
-      <c r="E43" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F43" t="str">
-        <v>g</v>
+      <c r="B43" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" t="s">
+        <v>23</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2785,14 +3595,14 @@
       <c r="K43">
         <v>7</v>
       </c>
-      <c r="L43" t="str">
-        <v>酸枣仁灵芝石斛膏</v>
-      </c>
-      <c r="M43" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N43" t="str">
-        <v>药材</v>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>30</v>
       </c>
       <c r="O43">
         <v>11.9</v>
@@ -2806,25 +3616,28 @@
       <c r="R43">
         <v>7</v>
       </c>
-    </row>
-    <row r="44">
+      <c r="S43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>49</v>
       </c>
-      <c r="B44" t="str">
-        <v>7af62f84...</v>
-      </c>
-      <c r="C44" t="str">
-        <v>栀子</v>
-      </c>
-      <c r="D44" t="str">
-        <v>AC</v>
-      </c>
-      <c r="E44" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F44" t="str">
-        <v>g</v>
+      <c r="B44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2841,14 +3654,14 @@
       <c r="K44">
         <v>5</v>
       </c>
-      <c r="L44" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M44" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N44" t="str">
-        <v>药材</v>
+      <c r="L44" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>30</v>
       </c>
       <c r="O44">
         <v>2.9</v>
@@ -2862,25 +3675,28 @@
       <c r="R44">
         <v>5</v>
       </c>
-    </row>
-    <row r="45">
+      <c r="S44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>50</v>
       </c>
-      <c r="B45" t="str">
-        <v>cf6a560c...</v>
-      </c>
-      <c r="C45" t="str">
-        <v>重瓣红玫瑰</v>
-      </c>
-      <c r="D45" t="str">
-        <v>PXWX</v>
-      </c>
-      <c r="E45" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F45" t="str">
-        <v>g</v>
+      <c r="B45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" t="s">
+        <v>23</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2894,17 +3710,17 @@
       <c r="J45">
         <v>68</v>
       </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v>沫彐淳膏</v>
-      </c>
-      <c r="M45" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N45" t="str">
-        <v>药材</v>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>30</v>
       </c>
       <c r="O45">
         <v>8.5</v>
@@ -2918,25 +3734,28 @@
       <c r="R45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46">
+      <c r="S45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>51</v>
       </c>
-      <c r="B46" t="str">
-        <v>84dc838a...</v>
-      </c>
-      <c r="C46" t="str">
-        <v>重瓣玫瑰花</v>
-      </c>
-      <c r="D46" t="str">
-        <v>PXXM</v>
-      </c>
-      <c r="E46" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F46" t="str">
-        <v>g</v>
+      <c r="B46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" t="s">
+        <v>162</v>
+      </c>
+      <c r="E46" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" t="s">
+        <v>23</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2950,17 +3769,17 @@
       <c r="J46">
         <v>68</v>
       </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
-        <v>佛手玫苓膏</v>
-      </c>
-      <c r="M46" t="str">
-        <v>2026-04-25T01:19:54</v>
-      </c>
-      <c r="N46" t="str">
-        <v>药材</v>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" t="s">
+        <v>66</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>30</v>
       </c>
       <c r="O46">
         <v>8.5</v>
@@ -2974,25 +3793,28 @@
       <c r="R46">
         <v>70</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="S46">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>52</v>
       </c>
-      <c r="B47" t="str">
-        <v>15acc31e48bd017035fc30f4</v>
-      </c>
-      <c r="C47" t="str">
-        <v>淡竹叶</v>
-      </c>
-      <c r="D47" t="str">
-        <v>DZY</v>
-      </c>
-      <c r="E47" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F47" t="str">
-        <v>g</v>
+      <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" t="s">
+        <v>165</v>
+      </c>
+      <c r="E47" t="s">
+        <v>166</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3009,14 +3831,14 @@
       <c r="K47">
         <v>0</v>
       </c>
-      <c r="L47" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M47" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N47" t="str">
-        <v>原料</v>
+      <c r="L47" t="s">
+        <v>91</v>
+      </c>
+      <c r="M47" t="s">
+        <v>167</v>
+      </c>
+      <c r="N47" t="s">
+        <v>166</v>
       </c>
       <c r="O47">
         <v>12.2</v>
@@ -3030,25 +3852,28 @@
       <c r="R47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48">
+      <c r="S47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>53</v>
       </c>
-      <c r="B48" t="str">
-        <v>7b95282de34daf3b3a5ce3c6</v>
-      </c>
-      <c r="C48" t="str">
-        <v>槐花</v>
-      </c>
-      <c r="D48" t="str">
-        <v>HH</v>
-      </c>
-      <c r="E48" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F48" t="str">
-        <v>g</v>
+      <c r="B48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" t="s">
+        <v>166</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -3063,16 +3888,16 @@
         <v>17</v>
       </c>
       <c r="K48">
-        <v>2.2</v>
-      </c>
-      <c r="L48" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M48" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N48" t="str">
-        <v>原料</v>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L48" t="s">
+        <v>91</v>
+      </c>
+      <c r="M48" t="s">
+        <v>167</v>
+      </c>
+      <c r="N48" t="s">
+        <v>166</v>
       </c>
       <c r="O48">
         <v>3.1</v>
@@ -3084,27 +3909,30 @@
         <v>17</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>54</v>
       </c>
-      <c r="B49" t="str">
-        <v>facb99f9c8f41399941bb499</v>
-      </c>
-      <c r="C49" t="str">
-        <v>马齿苋</v>
-      </c>
-      <c r="D49" t="str">
-        <v>MCX</v>
-      </c>
-      <c r="E49" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F49" t="str">
-        <v>g</v>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" t="s">
+        <v>166</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -3121,14 +3949,14 @@
       <c r="K49">
         <v>45</v>
       </c>
-      <c r="L49" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M49" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N49" t="str">
-        <v>原料</v>
+      <c r="L49" t="s">
+        <v>91</v>
+      </c>
+      <c r="M49" t="s">
+        <v>167</v>
+      </c>
+      <c r="N49" t="s">
+        <v>166</v>
       </c>
       <c r="O49">
         <v>1.3</v>
@@ -3142,25 +3970,28 @@
       <c r="R49">
         <v>45</v>
       </c>
-    </row>
-    <row r="50">
+      <c r="S49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>55</v>
       </c>
-      <c r="B50" t="str">
-        <v>5a4389b30d8fda3c09180882</v>
-      </c>
-      <c r="C50" t="str">
-        <v>薏苡仁</v>
-      </c>
-      <c r="D50" t="str">
-        <v>YYR</v>
-      </c>
-      <c r="E50" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F50" t="str">
-        <v>g</v>
+      <c r="B50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" t="s">
+        <v>176</v>
+      </c>
+      <c r="E50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -3177,14 +4008,14 @@
       <c r="K50">
         <v>15</v>
       </c>
-      <c r="L50" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M50" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N50" t="str">
-        <v>原料</v>
+      <c r="L50" t="s">
+        <v>91</v>
+      </c>
+      <c r="M50" t="s">
+        <v>167</v>
+      </c>
+      <c r="N50" t="s">
+        <v>166</v>
       </c>
       <c r="O50">
         <v>0.8</v>
@@ -3198,25 +4029,28 @@
       <c r="R50">
         <v>15</v>
       </c>
-    </row>
-    <row r="51">
+      <c r="S50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>56</v>
       </c>
-      <c r="B51" t="str">
-        <v>1eb648aad7da3913bdf223cb</v>
-      </c>
-      <c r="C51" t="str">
-        <v>莱菔子</v>
-      </c>
-      <c r="D51" t="str">
-        <v>LFZ</v>
-      </c>
-      <c r="E51" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F51" t="str">
-        <v>g</v>
+      <c r="B51" t="s">
+        <v>177</v>
+      </c>
+      <c r="C51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" t="s">
+        <v>179</v>
+      </c>
+      <c r="E51" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" t="s">
+        <v>23</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -3228,19 +4062,19 @@
         <v>30</v>
       </c>
       <c r="J51">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="K51">
         <v>4</v>
       </c>
-      <c r="L51" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M51" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N51" t="str">
-        <v>原料</v>
+      <c r="L51" t="s">
+        <v>91</v>
+      </c>
+      <c r="M51" t="s">
+        <v>167</v>
+      </c>
+      <c r="N51" t="s">
+        <v>166</v>
       </c>
       <c r="O51">
         <v>18.8</v>
@@ -3249,30 +4083,33 @@
         <v>30</v>
       </c>
       <c r="Q51">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="R51">
         <v>70</v>
       </c>
-    </row>
-    <row r="52">
+      <c r="S51">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>57</v>
       </c>
-      <c r="B52" t="str">
-        <v>e1c4bd9437d549325317d99a</v>
-      </c>
-      <c r="C52" t="str">
-        <v>山楂</v>
-      </c>
-      <c r="D52" t="str">
-        <v>SZ</v>
-      </c>
-      <c r="E52" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F52" t="str">
-        <v>g</v>
+      <c r="B52" t="s">
+        <v>180</v>
+      </c>
+      <c r="C52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" t="s">
+        <v>182</v>
+      </c>
+      <c r="E52" t="s">
+        <v>166</v>
+      </c>
+      <c r="F52" t="s">
+        <v>23</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -3289,14 +4126,14 @@
       <c r="K52">
         <v>5</v>
       </c>
-      <c r="L52" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M52" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N52" t="str">
-        <v>原料</v>
+      <c r="L52" t="s">
+        <v>91</v>
+      </c>
+      <c r="M52" t="s">
+        <v>167</v>
+      </c>
+      <c r="N52" t="s">
+        <v>166</v>
       </c>
       <c r="O52">
         <v>0.5</v>
@@ -3310,25 +4147,28 @@
       <c r="R52">
         <v>70</v>
       </c>
-    </row>
-    <row r="53">
+      <c r="S52">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>58</v>
       </c>
-      <c r="B53" t="str">
-        <v>110ae8b9091d24dc7c127214</v>
-      </c>
-      <c r="C53" t="str">
-        <v>麦芽</v>
-      </c>
-      <c r="D53" t="str">
-        <v>MY</v>
-      </c>
-      <c r="E53" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F53" t="str">
-        <v>g</v>
+      <c r="B53" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" t="s">
+        <v>184</v>
+      </c>
+      <c r="D53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" t="s">
+        <v>23</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -3345,14 +4185,14 @@
       <c r="K53">
         <v>11</v>
       </c>
-      <c r="L53" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M53" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N53" t="str">
-        <v>辅料</v>
+      <c r="L53" t="s">
+        <v>91</v>
+      </c>
+      <c r="M53" t="s">
+        <v>167</v>
+      </c>
+      <c r="N53" t="s">
+        <v>22</v>
       </c>
       <c r="O53">
         <v>10.3</v>
@@ -3366,25 +4206,28 @@
       <c r="R53">
         <v>11</v>
       </c>
-    </row>
-    <row r="54">
+      <c r="S53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>59</v>
       </c>
-      <c r="B54" t="str">
-        <v>78e72df182152ba6989ebf44</v>
-      </c>
-      <c r="C54" t="str">
-        <v>杏仁</v>
-      </c>
-      <c r="D54" t="str">
-        <v>XR</v>
-      </c>
-      <c r="E54" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F54" t="str">
-        <v>g</v>
+      <c r="B54" t="s">
+        <v>186</v>
+      </c>
+      <c r="C54" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" t="s">
+        <v>188</v>
+      </c>
+      <c r="E54" t="s">
+        <v>166</v>
+      </c>
+      <c r="F54" t="s">
+        <v>23</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -3401,14 +4244,14 @@
       <c r="K54">
         <v>8</v>
       </c>
-      <c r="L54" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M54" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N54" t="str">
-        <v>原料</v>
+      <c r="L54" t="s">
+        <v>91</v>
+      </c>
+      <c r="M54" t="s">
+        <v>167</v>
+      </c>
+      <c r="N54" t="s">
+        <v>166</v>
       </c>
       <c r="O54">
         <v>22.5</v>
@@ -3422,25 +4265,28 @@
       <c r="R54">
         <v>8</v>
       </c>
-    </row>
-    <row r="55">
+      <c r="S54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>60</v>
       </c>
-      <c r="B55" t="str">
-        <v>e9a993eab42b596bec2f1605</v>
-      </c>
-      <c r="C55" t="str">
-        <v>火麻仁</v>
-      </c>
-      <c r="D55" t="str">
-        <v>HMR</v>
-      </c>
-      <c r="E55" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F55" t="str">
-        <v>g</v>
+      <c r="B55" t="s">
+        <v>189</v>
+      </c>
+      <c r="C55" t="s">
+        <v>190</v>
+      </c>
+      <c r="D55" t="s">
+        <v>191</v>
+      </c>
+      <c r="E55" t="s">
+        <v>166</v>
+      </c>
+      <c r="F55" t="s">
+        <v>23</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -3457,14 +4303,14 @@
       <c r="K55">
         <v>0</v>
       </c>
-      <c r="L55" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M55" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N55" t="str">
-        <v>原料</v>
+      <c r="L55" t="s">
+        <v>91</v>
+      </c>
+      <c r="M55" t="s">
+        <v>167</v>
+      </c>
+      <c r="N55" t="s">
+        <v>166</v>
       </c>
       <c r="O55">
         <v>34.6</v>
@@ -3478,25 +4324,28 @@
       <c r="R55">
         <v>55</v>
       </c>
-    </row>
-    <row r="56">
+      <c r="S55">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>61</v>
       </c>
-      <c r="B56" t="str">
-        <v>e78e9bea50577e3e826b320c</v>
-      </c>
-      <c r="C56" t="str">
-        <v>鱼腥草</v>
-      </c>
-      <c r="D56" t="str">
-        <v>YXC</v>
-      </c>
-      <c r="E56" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F56" t="str">
-        <v>g</v>
+      <c r="B56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C56" t="s">
+        <v>193</v>
+      </c>
+      <c r="D56" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56" t="s">
+        <v>166</v>
+      </c>
+      <c r="F56" t="s">
+        <v>23</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -3513,14 +4362,14 @@
       <c r="K56">
         <v>21</v>
       </c>
-      <c r="L56" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M56" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N56" t="str">
-        <v>原料</v>
+      <c r="L56" t="s">
+        <v>91</v>
+      </c>
+      <c r="M56" t="s">
+        <v>167</v>
+      </c>
+      <c r="N56" t="s">
+        <v>166</v>
       </c>
       <c r="O56">
         <v>8</v>
@@ -3534,25 +4383,28 @@
       <c r="R56">
         <v>21</v>
       </c>
-    </row>
-    <row r="57">
+      <c r="S56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>62</v>
       </c>
-      <c r="B57" t="str">
-        <v>08cb40e51c88a479b73ee8e0</v>
-      </c>
-      <c r="C57" t="str">
-        <v>赤小豆</v>
-      </c>
-      <c r="D57" t="str">
-        <v>CXD</v>
-      </c>
-      <c r="E57" t="str">
-        <v>原料</v>
-      </c>
-      <c r="F57" t="str">
-        <v>g</v>
+      <c r="B57" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" t="s">
+        <v>197</v>
+      </c>
+      <c r="E57" t="s">
+        <v>166</v>
+      </c>
+      <c r="F57" t="s">
+        <v>23</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -3569,14 +4421,14 @@
       <c r="K57">
         <v>2</v>
       </c>
-      <c r="L57" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M57" t="str">
-        <v>2026-04-25 04:27:25</v>
-      </c>
-      <c r="N57" t="str">
-        <v>原料</v>
+      <c r="L57" t="s">
+        <v>91</v>
+      </c>
+      <c r="M57" t="s">
+        <v>167</v>
+      </c>
+      <c r="N57" t="s">
+        <v>166</v>
       </c>
       <c r="O57">
         <v>20.2</v>
@@ -3590,25 +4442,28 @@
       <c r="R57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58">
+      <c r="S57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>63</v>
       </c>
-      <c r="B58" t="str">
-        <v>MAT_dfd71344_225cc5</v>
-      </c>
-      <c r="C58" t="str">
-        <v>阿胶</v>
-      </c>
-      <c r="D58" t="str">
-        <v>EJ</v>
-      </c>
-      <c r="E58" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F58" t="str">
-        <v>g</v>
+      <c r="B58" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -3625,14 +4480,14 @@
       <c r="K58">
         <v>46</v>
       </c>
-      <c r="L58" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M58" t="str">
-        <v>2026-04-25 02:55:21</v>
-      </c>
-      <c r="N58" t="str">
-        <v>辅料</v>
+      <c r="L58" t="s">
+        <v>91</v>
+      </c>
+      <c r="M58" t="s">
+        <v>199</v>
+      </c>
+      <c r="N58" t="s">
+        <v>22</v>
       </c>
       <c r="O58">
         <v>10.5</v>
@@ -3646,25 +4501,28 @@
       <c r="R58">
         <v>46</v>
       </c>
-    </row>
-    <row r="59">
+      <c r="S58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>64</v>
       </c>
-      <c r="B59" t="str">
-        <v>MAT_e9eabdcd4eb047</v>
-      </c>
-      <c r="C59" t="str">
-        <v>桑葫鲜果</v>
-      </c>
-      <c r="D59" t="str">
-        <v>SSXG</v>
-      </c>
-      <c r="E59" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F59" t="str">
-        <v>g</v>
+      <c r="B59" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" t="s">
+        <v>201</v>
+      </c>
+      <c r="D59" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -3681,14 +4539,14 @@
       <c r="K59">
         <v>45</v>
       </c>
-      <c r="L59" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M59" t="str">
-        <v>2026-04-25T23:53:31.421Z</v>
-      </c>
-      <c r="N59" t="str">
-        <v>辅料</v>
+      <c r="L59" t="s">
+        <v>91</v>
+      </c>
+      <c r="M59" t="s">
+        <v>203</v>
+      </c>
+      <c r="N59" t="s">
+        <v>22</v>
       </c>
       <c r="O59">
         <v>1.3</v>
@@ -3702,25 +4560,28 @@
       <c r="R59">
         <v>45</v>
       </c>
-    </row>
-    <row r="60">
+      <c r="S59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>65</v>
       </c>
-      <c r="B60" t="str">
-        <v>MAT_72387001c4964d</v>
-      </c>
-      <c r="C60" t="str">
-        <v>酸枣蜜炼</v>
-      </c>
-      <c r="D60" t="str">
-        <v>SZML</v>
-      </c>
-      <c r="E60" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F60" t="str">
-        <v>g</v>
+      <c r="B60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D60" t="s">
+        <v>206</v>
+      </c>
+      <c r="E60" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -3737,14 +4598,14 @@
       <c r="K60">
         <v>15</v>
       </c>
-      <c r="L60" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M60" t="str">
-        <v>2026-04-25T23:53:31.421Z</v>
-      </c>
-      <c r="N60" t="str">
-        <v>辅料</v>
+      <c r="L60" t="s">
+        <v>91</v>
+      </c>
+      <c r="M60" t="s">
+        <v>203</v>
+      </c>
+      <c r="N60" t="s">
+        <v>22</v>
       </c>
       <c r="O60">
         <v>0.8</v>
@@ -3758,25 +4619,28 @@
       <c r="R60">
         <v>15</v>
       </c>
-    </row>
-    <row r="61">
+      <c r="S60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>66</v>
       </c>
-      <c r="B61" t="str">
-        <v>MAT_b590e0058b6b4f</v>
-      </c>
-      <c r="C61" t="str">
-        <v>黄精蜜炼</v>
-      </c>
-      <c r="D61" t="str">
-        <v>HJML</v>
-      </c>
-      <c r="E61" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F61" t="str">
-        <v>g</v>
+      <c r="B61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" t="s">
+        <v>209</v>
+      </c>
+      <c r="E61" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -3788,19 +4652,19 @@
         <v>30</v>
       </c>
       <c r="J61">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="K61">
         <v>4</v>
       </c>
-      <c r="L61" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M61" t="str">
-        <v>2026-04-25T23:53:31.421Z</v>
-      </c>
-      <c r="N61" t="str">
-        <v>辅料</v>
+      <c r="L61" t="s">
+        <v>91</v>
+      </c>
+      <c r="M61" t="s">
+        <v>203</v>
+      </c>
+      <c r="N61" t="s">
+        <v>22</v>
       </c>
       <c r="O61">
         <v>18.8</v>
@@ -3809,30 +4673,33 @@
         <v>30</v>
       </c>
       <c r="Q61">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="R61">
         <v>4</v>
       </c>
-    </row>
-    <row r="62">
+      <c r="S61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>67</v>
       </c>
-      <c r="B62" t="str">
-        <v>MAT_11db658a0c8f49</v>
-      </c>
-      <c r="C62" t="str">
-        <v>薄荷</v>
-      </c>
-      <c r="D62" t="str">
-        <v>BH2</v>
-      </c>
-      <c r="E62" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F62" t="str">
-        <v>g</v>
+      <c r="B62" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" t="s">
+        <v>211</v>
+      </c>
+      <c r="D62" t="s">
+        <v>212</v>
+      </c>
+      <c r="E62" t="s">
+        <v>30</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -3849,14 +4716,14 @@
       <c r="K62">
         <v>5</v>
       </c>
-      <c r="L62" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M62" t="str">
-        <v>2026-04-25T23:53:31.421Z</v>
-      </c>
-      <c r="N62" t="str">
-        <v>药材</v>
+      <c r="L62" t="s">
+        <v>91</v>
+      </c>
+      <c r="M62" t="s">
+        <v>203</v>
+      </c>
+      <c r="N62" t="s">
+        <v>30</v>
       </c>
       <c r="O62">
         <v>0.5</v>
@@ -3870,25 +4737,28 @@
       <c r="R62">
         <v>5</v>
       </c>
-    </row>
-    <row r="63">
+      <c r="S62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>68</v>
       </c>
-      <c r="B63" t="str">
-        <v>MAT_765a53ebb2784e</v>
-      </c>
-      <c r="C63" t="str">
-        <v>麦冬</v>
-      </c>
-      <c r="D63" t="str">
-        <v>MD</v>
-      </c>
-      <c r="E63" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F63" t="str">
-        <v>g</v>
+      <c r="B63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -3905,14 +4775,14 @@
       <c r="K63">
         <v>21</v>
       </c>
-      <c r="L63" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M63" t="str">
-        <v>2026-04-25T23:53:31.421Z</v>
-      </c>
-      <c r="N63" t="str">
-        <v>药材</v>
+      <c r="L63" t="s">
+        <v>91</v>
+      </c>
+      <c r="M63" t="s">
+        <v>203</v>
+      </c>
+      <c r="N63" t="s">
+        <v>30</v>
       </c>
       <c r="O63">
         <v>8</v>
@@ -3926,25 +4796,28 @@
       <c r="R63">
         <v>21</v>
       </c>
-    </row>
-    <row r="64">
+      <c r="S63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>69</v>
       </c>
-      <c r="B64" t="str">
-        <v>MAT_e6d32d4c4e134f</v>
-      </c>
-      <c r="C64" t="str">
-        <v>白术</v>
-      </c>
-      <c r="D64" t="str">
-        <v>BS2</v>
-      </c>
-      <c r="E64" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F64" t="str">
-        <v>g</v>
+      <c r="B64" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" t="s">
+        <v>217</v>
+      </c>
+      <c r="D64" t="s">
+        <v>218</v>
+      </c>
+      <c r="E64" t="s">
+        <v>30</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3961,14 +4834,14 @@
       <c r="K64">
         <v>2</v>
       </c>
-      <c r="L64" t="str">
-        <v>刘明膏滋营养成分表20260303</v>
-      </c>
-      <c r="M64" t="str">
-        <v>2026-04-25T23:53:31.421Z</v>
-      </c>
-      <c r="N64" t="str">
-        <v>药材</v>
+      <c r="L64" t="s">
+        <v>91</v>
+      </c>
+      <c r="M64" t="s">
+        <v>203</v>
+      </c>
+      <c r="N64" t="s">
+        <v>30</v>
       </c>
       <c r="O64">
         <v>20.2</v>
@@ -3982,10 +4855,16 @@
       <c r="R64">
         <v>2</v>
       </c>
+      <c r="S64" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R64"/>
+    <ignoredError sqref="A1:S1 A19:S23 A18:R18 A3:S16 A2:R2 A25:S64 A24:R24 A17:R17" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test/原料数据库导入_完整版_已清理.xlsx
+++ b/test/原料数据库导入_完整版_已清理.xlsx
@@ -1,46 +1,320 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramData\workspace-codeby\ting-studio\test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088544DD-8F8B-48A8-962E-AD53701FE1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="原料数据" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>原料名称</t>
+  </si>
+  <si>
+    <t>编码</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>库存</t>
+  </si>
+  <si>
+    <t>蛋白质(g/100g)</t>
+  </si>
+  <si>
+    <t>脂肪(g/100g)</t>
+  </si>
+  <si>
+    <t>碳水化合物(g/100g)</t>
+  </si>
+  <si>
+    <t>钠(mg/100g)</t>
+  </si>
+  <si>
+    <t>单价(元/kg)</t>
+  </si>
+  <si>
+    <t>数据来源</t>
+  </si>
+  <si>
+    <t>栀子</t>
+  </si>
+  <si>
+    <t>药材</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>full_reimport</t>
+  </si>
+  <si>
+    <t>百合</t>
+  </si>
+  <si>
+    <t>薄荷</t>
+  </si>
+  <si>
+    <t>白术</t>
+  </si>
+  <si>
+    <t>陈皮</t>
+  </si>
+  <si>
+    <t>赤小豆</t>
+  </si>
+  <si>
+    <t>桑椹</t>
+  </si>
+  <si>
+    <t>当归</t>
+  </si>
+  <si>
+    <t>党参</t>
+  </si>
+  <si>
+    <t>淡竹叶</t>
+  </si>
+  <si>
+    <t>阿胶</t>
+  </si>
+  <si>
+    <t>辅料</t>
+  </si>
+  <si>
+    <t>葛根</t>
+  </si>
+  <si>
+    <t>茯苓</t>
+  </si>
+  <si>
+    <t>佛手</t>
+  </si>
+  <si>
+    <t>甘草</t>
+  </si>
+  <si>
+    <t>枸杞子</t>
+  </si>
+  <si>
+    <t>桔梗</t>
+  </si>
+  <si>
+    <t>槐花</t>
+  </si>
+  <si>
+    <t>沙棘</t>
+  </si>
+  <si>
+    <t>黄精</t>
+  </si>
+  <si>
+    <t>黄精蜜炼</t>
+  </si>
+  <si>
+    <t>火麻仁</t>
+  </si>
+  <si>
+    <t>黄芪</t>
+  </si>
+  <si>
+    <t>藿香</t>
+  </si>
+  <si>
+    <t>香橼</t>
+  </si>
+  <si>
+    <t>金银花</t>
+  </si>
+  <si>
+    <t>炒白扁豆</t>
+  </si>
+  <si>
+    <t>小麦</t>
+  </si>
+  <si>
+    <t>莱菔子</t>
+  </si>
+  <si>
+    <t>荷叶</t>
+  </si>
+  <si>
+    <t>小茴香</t>
+  </si>
+  <si>
+    <t>莲子</t>
+  </si>
+  <si>
+    <t>灵芝</t>
+  </si>
+  <si>
+    <t>牡蛎</t>
+  </si>
+  <si>
+    <t>昆布</t>
+  </si>
+  <si>
+    <t>丹凤牡丹花</t>
+  </si>
+  <si>
+    <t>姜黄</t>
+  </si>
+  <si>
+    <t>山茱萸</t>
+  </si>
+  <si>
+    <t>蒲公英</t>
+  </si>
+  <si>
+    <t>鸡内金</t>
+  </si>
+  <si>
+    <t>芦根</t>
+  </si>
+  <si>
+    <t>化橘红</t>
+  </si>
+  <si>
+    <t>乌药叶</t>
+  </si>
+  <si>
+    <t>黄芥子</t>
+  </si>
+  <si>
+    <t>苦杏仁</t>
+  </si>
+  <si>
+    <t>西洋参</t>
+  </si>
+  <si>
+    <t>马齿苋</t>
+  </si>
+  <si>
+    <t>麦冬</t>
+  </si>
+  <si>
+    <t>地龙蛋白肽粉</t>
+  </si>
+  <si>
+    <t>麦芽</t>
+  </si>
+  <si>
+    <t>纳豆</t>
+  </si>
+  <si>
+    <t>肉豆蔻</t>
+  </si>
+  <si>
+    <t>肉桂</t>
+  </si>
+  <si>
+    <t>重瓣红玫瑰</t>
+  </si>
+  <si>
+    <t>重瓣玫瑰花</t>
+  </si>
+  <si>
+    <t>芡实</t>
+  </si>
+  <si>
+    <t>白芷</t>
+  </si>
+  <si>
+    <t>草果</t>
+  </si>
+  <si>
+    <t>铁皮石斛</t>
+  </si>
+  <si>
+    <t>显脉旋覆花</t>
+  </si>
+  <si>
+    <t>桑葫鲜果</t>
+  </si>
+  <si>
+    <t>山药</t>
+  </si>
+  <si>
+    <t>山楂</t>
+  </si>
+  <si>
+    <t>酸枣蜜炼</t>
+  </si>
+  <si>
+    <t>酸枣仁</t>
+  </si>
+  <si>
+    <t>桃仁</t>
+  </si>
+  <si>
+    <t>大枣</t>
+  </si>
+  <si>
+    <t>短梗五加</t>
+  </si>
+  <si>
+    <t>西红花</t>
+  </si>
+  <si>
+    <t>低聚异麦芽糖</t>
+  </si>
+  <si>
+    <t>杏仁</t>
+  </si>
+  <si>
+    <t>乌梅</t>
+  </si>
+  <si>
+    <t>鱼腥草</t>
+  </si>
+  <si>
+    <t>薏苡仁</t>
+  </si>
+  <si>
+    <t>平卧菊三七</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -65,13 +339,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,83 +678,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M76"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="6.83203125" customWidth="1"/>
-    <col min="7" max="7" width="6.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="7" width="6.875" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="9" width="14.875" customWidth="1"/>
+    <col min="10" max="10" width="18.875" customWidth="1"/>
+    <col min="11" max="11" width="14.875" customWidth="1"/>
+    <col min="12" max="12" width="12.875" customWidth="1"/>
+    <col min="13" max="13" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>原料名称</v>
-      </c>
-      <c r="D1" t="str">
-        <v>编码</v>
-      </c>
-      <c r="E1" t="str">
-        <v>类型</v>
-      </c>
-      <c r="F1" t="str">
-        <v>单位</v>
-      </c>
-      <c r="G1" t="str">
-        <v>库存</v>
-      </c>
-      <c r="H1" t="str">
-        <v>蛋白质(g/100g)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>脂肪(g/100g)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>碳水化合物(g/100g)</v>
-      </c>
-      <c r="K1" t="str">
-        <v>钠(mg/100g)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>单价(元/kg)</v>
-      </c>
-      <c r="M1" t="str">
-        <v>数据来源</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>moldtk2r9ecc6n83</v>
-      </c>
-      <c r="C2" t="str">
-        <v>栀子</v>
-      </c>
-      <c r="D2" t="str">
-        <v>AC</v>
-      </c>
-      <c r="E2" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F2" t="str">
-        <v>g</v>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -490,30 +766,24 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>moldtk2osz19b9yo</v>
-      </c>
-      <c r="C3" t="str">
-        <v>百合</v>
-      </c>
-      <c r="D3" t="str">
-        <v>BH</v>
-      </c>
-      <c r="E3" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F3" t="str">
-        <v>g</v>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -533,28 +803,22 @@
       <c r="L3">
         <v>48</v>
       </c>
-      <c r="M3" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>moldtk2s7w6pr250</v>
-      </c>
-      <c r="C4" t="str">
-        <v>薄荷</v>
-      </c>
-      <c r="D4" t="str">
-        <v>BH2</v>
-      </c>
-      <c r="E4" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F4" t="str">
-        <v>g</v>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -572,30 +836,24 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>11</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>moldtk2sxaig296o</v>
-      </c>
-      <c r="C5" t="str">
-        <v>白术</v>
-      </c>
-      <c r="D5" t="str">
-        <v>BS2</v>
-      </c>
-      <c r="E5" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F5" t="str">
-        <v>g</v>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -613,30 +871,24 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>11</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>moldtk2ptyunea0e</v>
-      </c>
-      <c r="C6" t="str">
-        <v>陈皮</v>
-      </c>
-      <c r="D6" t="str">
-        <v>CP</v>
-      </c>
-      <c r="E6" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F6" t="str">
-        <v>g</v>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -656,28 +908,22 @@
       <c r="L6">
         <v>15</v>
       </c>
-      <c r="M6" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>moldtk2r1otznhcm</v>
-      </c>
-      <c r="C7" t="str">
-        <v>赤小豆</v>
-      </c>
-      <c r="D7" t="str">
-        <v>CXD</v>
-      </c>
-      <c r="E7" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F7" t="str">
-        <v>g</v>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -695,30 +941,24 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>11</v>
+      </c>
+      <c r="M7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>moldtk2qk71vfo7t</v>
-      </c>
-      <c r="C8" t="str">
-        <v>桑椹</v>
-      </c>
-      <c r="D8" t="str">
-        <v>DB</v>
-      </c>
-      <c r="E8" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F8" t="str">
-        <v>g</v>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -736,30 +976,24 @@
         <v>2</v>
       </c>
       <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>11</v>
+      </c>
+      <c r="M8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>moldtk2p466c6wbu</v>
-      </c>
-      <c r="C9" t="str">
-        <v>当归</v>
-      </c>
-      <c r="D9" t="str">
-        <v>DG</v>
-      </c>
-      <c r="E9" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F9" t="str">
-        <v>g</v>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -779,28 +1013,22 @@
       <c r="L9">
         <v>130</v>
       </c>
-      <c r="M9" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>moldtk2ptgb4b5xs</v>
-      </c>
-      <c r="C10" t="str">
-        <v>党参</v>
-      </c>
-      <c r="D10" t="str">
-        <v>DS</v>
-      </c>
-      <c r="E10" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F10" t="str">
-        <v>g</v>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -818,30 +1046,24 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>11</v>
+      </c>
+      <c r="M10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>moldtk2rjyjld71n</v>
-      </c>
-      <c r="C11" t="str">
-        <v>淡竹叶</v>
-      </c>
-      <c r="D11" t="str">
-        <v>DZY</v>
-      </c>
-      <c r="E11" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F11" t="str">
-        <v>g</v>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -859,30 +1081,24 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>11</v>
+      </c>
+      <c r="M11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>moldtk2o7up69cxx</v>
-      </c>
-      <c r="C12" t="str">
-        <v>阿胶</v>
-      </c>
-      <c r="D12" t="str">
-        <v>EJ</v>
-      </c>
-      <c r="E12" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F12" t="str">
-        <v>g</v>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -900,30 +1116,24 @@
         <v>46</v>
       </c>
       <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>11</v>
+      </c>
+      <c r="M12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>moldtk2p9b80pn08</v>
-      </c>
-      <c r="C13" t="str">
-        <v>葛根</v>
-      </c>
-      <c r="D13" t="str">
-        <v>FF</v>
-      </c>
-      <c r="E13" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F13" t="str">
-        <v>g</v>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -941,30 +1151,24 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>11</v>
+      </c>
+      <c r="M13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>moldtk2p9v68i3ag</v>
-      </c>
-      <c r="C14" t="str">
-        <v>茯苓</v>
-      </c>
-      <c r="D14" t="str">
-        <v>FL</v>
-      </c>
-      <c r="E14" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F14" t="str">
-        <v>g</v>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -984,28 +1188,22 @@
       <c r="L14">
         <v>35</v>
       </c>
-      <c r="M14" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="M14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>moldtk2pmdo0q9zu</v>
-      </c>
-      <c r="C15" t="str">
-        <v>佛手</v>
-      </c>
-      <c r="D15" t="str">
-        <v>FS</v>
-      </c>
-      <c r="E15" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F15" t="str">
-        <v>g</v>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1025,34 +1223,28 @@
       <c r="L15">
         <v>60</v>
       </c>
-      <c r="M15" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>moldtk2pvhlks1ov</v>
-      </c>
-      <c r="C16" t="str">
-        <v>甘草</v>
-      </c>
-      <c r="D16" t="str">
-        <v>GC</v>
-      </c>
-      <c r="E16" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F16" t="str">
-        <v>g</v>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I16">
         <v>4.2</v>
@@ -1066,28 +1258,22 @@
       <c r="L16">
         <v>40</v>
       </c>
-      <c r="M16" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="M16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>moldtk2pto2jng8i</v>
-      </c>
-      <c r="C17" t="str">
-        <v>枸杞子</v>
-      </c>
-      <c r="D17" t="str">
-        <v>GUC</v>
-      </c>
-      <c r="E17" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F17" t="str">
-        <v>g</v>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1099,36 +1285,30 @@
         <v>1.5</v>
       </c>
       <c r="J17">
-        <v>64.1</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="K17">
         <v>252</v>
       </c>
       <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>11</v>
+      </c>
+      <c r="M17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>moldtk2qpxez45g4</v>
-      </c>
-      <c r="C18" t="str">
-        <v>桔梗</v>
-      </c>
-      <c r="D18" t="str">
-        <v>GV</v>
-      </c>
-      <c r="E18" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F18" t="str">
-        <v>g</v>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1140,7 +1320,7 @@
         <v>0.9</v>
       </c>
       <c r="J18">
-        <v>74.6</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="K18">
         <v>12</v>
@@ -1148,28 +1328,22 @@
       <c r="L18">
         <v>56</v>
       </c>
-      <c r="M18" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="M18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>moldtk2r8hhnknxm</v>
-      </c>
-      <c r="C19" t="str">
-        <v>槐花</v>
-      </c>
-      <c r="D19" t="str">
-        <v>HH</v>
-      </c>
-      <c r="E19" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F19" t="str">
-        <v>g</v>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1184,33 +1358,27 @@
         <v>17</v>
       </c>
       <c r="K19">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>11</v>
+      </c>
+      <c r="M19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>moldtk2qu5cx95m0</v>
-      </c>
-      <c r="C20" t="str">
-        <v>沙棘</v>
-      </c>
-      <c r="D20" t="str">
-        <v>HI</v>
-      </c>
-      <c r="E20" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F20" t="str">
-        <v>g</v>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1228,30 +1396,24 @@
         <v>28</v>
       </c>
       <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>11</v>
+      </c>
+      <c r="M20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>moldtk2qx4es72j7</v>
-      </c>
-      <c r="C21" t="str">
-        <v>黄精</v>
-      </c>
-      <c r="D21" t="str">
-        <v>HJ</v>
-      </c>
-      <c r="E21" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F21" t="str">
-        <v>g</v>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1271,28 +1433,22 @@
       <c r="L21">
         <v>78</v>
       </c>
-      <c r="M21" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="M21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>moldtk2sclw0eorw</v>
-      </c>
-      <c r="C22" t="str">
-        <v>黄精蜜炼</v>
-      </c>
-      <c r="D22" t="str">
-        <v>HJML</v>
-      </c>
-      <c r="E22" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F22" t="str">
-        <v>g</v>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1304,36 +1460,30 @@
         <v>30</v>
       </c>
       <c r="J22">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="K22">
         <v>4</v>
       </c>
       <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>11</v>
+      </c>
+      <c r="M22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>moldtk2rcqyhbxl1</v>
-      </c>
-      <c r="C23" t="str">
-        <v>火麻仁</v>
-      </c>
-      <c r="D23" t="str">
-        <v>HMR</v>
-      </c>
-      <c r="E23" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F23" t="str">
-        <v>g</v>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1353,28 +1503,22 @@
       <c r="L23">
         <v>55</v>
       </c>
-      <c r="M23" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="M23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>moldtk2q4g1s2lld</v>
-      </c>
-      <c r="C24" t="str">
-        <v>黄芪</v>
-      </c>
-      <c r="D24" t="str">
-        <v>HQ</v>
-      </c>
-      <c r="E24" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F24" t="str">
-        <v>g</v>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1383,7 +1527,7 @@
         <v>14.9</v>
       </c>
       <c r="I24">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J24">
         <v>33.4</v>
@@ -1394,28 +1538,22 @@
       <c r="L24">
         <v>33</v>
       </c>
-      <c r="M24" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="M24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>moldtk2qqazq3x5v</v>
-      </c>
-      <c r="C25" t="str">
-        <v>藿香</v>
-      </c>
-      <c r="D25" t="str">
-        <v>JJ</v>
-      </c>
-      <c r="E25" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F25" t="str">
-        <v>g</v>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1433,30 +1571,24 @@
         <v>46</v>
       </c>
       <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>11</v>
+      </c>
+      <c r="M25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>moldtk2rxvy20hg5</v>
-      </c>
-      <c r="C26" t="str">
-        <v>香橼</v>
-      </c>
-      <c r="D26" t="str">
-        <v>JM</v>
-      </c>
-      <c r="E26" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F26" t="str">
-        <v>g</v>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1474,30 +1606,24 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>11</v>
+      </c>
+      <c r="M26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>moldtk2q2owg5sx4</v>
-      </c>
-      <c r="C27" t="str">
-        <v>金银花</v>
-      </c>
-      <c r="D27" t="str">
-        <v>JYH</v>
-      </c>
-      <c r="E27" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F27" t="str">
-        <v>g</v>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1509,36 +1635,30 @@
         <v>4.5</v>
       </c>
       <c r="J27">
-        <v>32.8</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>11</v>
+      </c>
+      <c r="M27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>moldtk2o3og7rf4h</v>
-      </c>
-      <c r="C28" t="str">
-        <v>炒白扁豆</v>
-      </c>
-      <c r="D28" t="str">
-        <v>KRLE</v>
-      </c>
-      <c r="E28" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F28" t="str">
-        <v>g</v>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1556,30 +1676,24 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>11</v>
+      </c>
+      <c r="M28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>moldtk2raavmgpbg</v>
-      </c>
-      <c r="C29" t="str">
-        <v>小麦</v>
-      </c>
-      <c r="D29" t="str">
-        <v>LC</v>
-      </c>
-      <c r="E29" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F29" t="str">
-        <v>g</v>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1597,30 +1711,24 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>11</v>
+      </c>
+      <c r="M29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>moldtk2rkn4nhgn7</v>
-      </c>
-      <c r="C30" t="str">
-        <v>莱菔子</v>
-      </c>
-      <c r="D30" t="str">
-        <v>LFZ</v>
-      </c>
-      <c r="E30" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F30" t="str">
-        <v>g</v>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1632,7 +1740,7 @@
         <v>30</v>
       </c>
       <c r="J30">
-        <v>37.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="K30">
         <v>4</v>
@@ -1640,28 +1748,22 @@
       <c r="L30">
         <v>70</v>
       </c>
-      <c r="M30" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="M30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>moldtk2po45jf5uu</v>
-      </c>
-      <c r="C31" t="str">
-        <v>荷叶</v>
-      </c>
-      <c r="D31" t="str">
-        <v>LS</v>
-      </c>
-      <c r="E31" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F31" t="str">
-        <v>g</v>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1679,30 +1781,24 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>11</v>
+      </c>
+      <c r="M31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>moldtk2rsjkmom31</v>
-      </c>
-      <c r="C32" t="str">
-        <v>小茴香</v>
-      </c>
-      <c r="D32" t="str">
-        <v>LWJ</v>
-      </c>
-      <c r="E32" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F32" t="str">
-        <v>g</v>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1720,30 +1816,24 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>11</v>
+      </c>
+      <c r="M32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>moldtk2qqzdxs1za</v>
-      </c>
-      <c r="C33" t="str">
-        <v>莲子</v>
-      </c>
-      <c r="D33" t="str">
-        <v>LZ</v>
-      </c>
-      <c r="E33" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F33" t="str">
-        <v>g</v>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1761,30 +1851,24 @@
         <v>5</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>11</v>
+      </c>
+      <c r="M33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>moldtk2q3zeewe3q</v>
-      </c>
-      <c r="C34" t="str">
-        <v>灵芝</v>
-      </c>
-      <c r="D34" t="str">
-        <v>LZ_25</v>
-      </c>
-      <c r="E34" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F34" t="str">
-        <v>g</v>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1793,7 +1877,7 @@
         <v>88.8</v>
       </c>
       <c r="I34">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J34">
         <v>4.7</v>
@@ -1802,30 +1886,24 @@
         <v>224</v>
       </c>
       <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>11</v>
+      </c>
+      <c r="M34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>moldtk2sa5pk3k90</v>
-      </c>
-      <c r="C35" t="str">
-        <v>牡蛎</v>
-      </c>
-      <c r="D35" t="str">
-        <v>MAT063</v>
-      </c>
-      <c r="E35" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F35" t="str">
-        <v>g</v>
+      <c r="C35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1843,30 +1921,24 @@
         <v>510</v>
       </c>
       <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>11</v>
+      </c>
+      <c r="M35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>moldtk2svjsn794o</v>
-      </c>
-      <c r="C36" t="str">
-        <v>昆布</v>
-      </c>
-      <c r="D36" t="str">
-        <v>MAT064</v>
-      </c>
-      <c r="E36" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F36" t="str">
-        <v>g</v>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1886,28 +1958,22 @@
       <c r="L36">
         <v>70</v>
       </c>
-      <c r="M36" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="M36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>moldtk2sw7ezh62t</v>
-      </c>
-      <c r="C37" t="str">
-        <v>丹凤牡丹花</v>
-      </c>
-      <c r="D37" t="str">
-        <v>MAT065</v>
-      </c>
-      <c r="E37" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F37" t="str">
-        <v>g</v>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1925,30 +1991,24 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>11</v>
+      </c>
+      <c r="M37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>moldtk2szbjfwk5b</v>
-      </c>
-      <c r="C38" t="str">
-        <v>姜黄</v>
-      </c>
-      <c r="D38" t="str">
-        <v>MAT066</v>
-      </c>
-      <c r="E38" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F38" t="str">
-        <v>g</v>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1960,36 +2020,30 @@
         <v>9.9</v>
       </c>
       <c r="J38">
-        <v>64.9</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="K38">
         <v>38</v>
       </c>
       <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>11</v>
+      </c>
+      <c r="M38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>moldtk2sqye71b0b</v>
-      </c>
-      <c r="C39" t="str">
-        <v>山茱萸</v>
-      </c>
-      <c r="D39" t="str">
-        <v>MAT067</v>
-      </c>
-      <c r="E39" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F39" t="str">
-        <v>g</v>
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2001,36 +2055,30 @@
         <v>1.5</v>
       </c>
       <c r="J39">
-        <v>64.1</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="K39">
         <v>252</v>
       </c>
       <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>11</v>
+      </c>
+      <c r="M39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>moldtk2santkokxx</v>
-      </c>
-      <c r="C40" t="str">
-        <v>蒲公英</v>
-      </c>
-      <c r="D40" t="str">
-        <v>MAT068</v>
-      </c>
-      <c r="E40" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F40" t="str">
-        <v>g</v>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -2039,7 +2087,7 @@
         <v>4.8</v>
       </c>
       <c r="I40">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J40">
         <v>7</v>
@@ -2050,28 +2098,22 @@
       <c r="L40">
         <v>70</v>
       </c>
-      <c r="M40" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="M40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>moldtk2skj8wnxup</v>
-      </c>
-      <c r="C41" t="str">
-        <v>鸡内金</v>
-      </c>
-      <c r="D41" t="str">
-        <v>MAT069</v>
-      </c>
-      <c r="E41" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F41" t="str">
-        <v>g</v>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2089,30 +2131,24 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>11</v>
+      </c>
+      <c r="M41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>moldtk2spzdnhdbb</v>
-      </c>
-      <c r="C42" t="str">
-        <v>芦根</v>
-      </c>
-      <c r="D42" t="str">
-        <v>MAT070</v>
-      </c>
-      <c r="E42" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F42" t="str">
-        <v>g</v>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -2130,30 +2166,24 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>11</v>
+      </c>
+      <c r="M42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>moldtk2snt4kmant</v>
-      </c>
-      <c r="C43" t="str">
-        <v>化橘红</v>
-      </c>
-      <c r="D43" t="str">
-        <v>MAT071</v>
-      </c>
-      <c r="E43" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F43" t="str">
-        <v>g</v>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2171,30 +2201,24 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>11</v>
+      </c>
+      <c r="M43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>moldtk2s027eibo8</v>
-      </c>
-      <c r="C44" t="str">
-        <v>乌药叶</v>
-      </c>
-      <c r="D44" t="str">
-        <v>MAT072</v>
-      </c>
-      <c r="E44" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F44" t="str">
-        <v>g</v>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s">
+        <v>15</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -2212,30 +2236,24 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>11</v>
+      </c>
+      <c r="M44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>moldtk2s3w1fmopp</v>
-      </c>
-      <c r="C45" t="str">
-        <v>黄芥子</v>
-      </c>
-      <c r="D45" t="str">
-        <v>MAT073</v>
-      </c>
-      <c r="E45" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F45" t="str">
-        <v>g</v>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2253,30 +2271,24 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>11</v>
+      </c>
+      <c r="M45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>moldtk2s9dvngp0a</v>
-      </c>
-      <c r="C46" t="str">
-        <v>苦杏仁</v>
-      </c>
-      <c r="D46" t="str">
-        <v>MAT074</v>
-      </c>
-      <c r="E46" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F46" t="str">
-        <v>g</v>
+      <c r="C46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2296,28 +2308,22 @@
       <c r="L46">
         <v>70</v>
       </c>
-      <c r="M46" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="M46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>moldtk2ttkdtk2vh</v>
-      </c>
-      <c r="C47" t="str">
-        <v>西洋参</v>
-      </c>
-      <c r="D47" t="str">
-        <v>MAT075</v>
-      </c>
-      <c r="E47" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F47" t="str">
-        <v>g</v>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2329,36 +2335,30 @@
         <v>0.3</v>
       </c>
       <c r="J47">
-        <v>65.6</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>11</v>
+      </c>
+      <c r="M47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>moldtk2rxbpju291</v>
-      </c>
-      <c r="C48" t="str">
-        <v>马齿苋</v>
-      </c>
-      <c r="D48" t="str">
-        <v>MCX</v>
-      </c>
-      <c r="E48" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F48" t="str">
-        <v>g</v>
+      <c r="C48" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2376,30 +2376,24 @@
         <v>45</v>
       </c>
       <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>11</v>
+      </c>
+      <c r="M48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>moldtk2s7m5mpt3n</v>
-      </c>
-      <c r="C49" t="str">
-        <v>麦冬</v>
-      </c>
-      <c r="D49" t="str">
-        <v>MD</v>
-      </c>
-      <c r="E49" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F49" t="str">
-        <v>g</v>
+      <c r="C49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2417,30 +2411,24 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>11</v>
+      </c>
+      <c r="M49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>moldtk2p4z69m0jm</v>
-      </c>
-      <c r="C50" t="str">
-        <v>地龙蛋白肽粉</v>
-      </c>
-      <c r="D50" t="str">
-        <v>MLFR</v>
-      </c>
-      <c r="E50" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F50" t="str">
-        <v>g</v>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2458,30 +2446,24 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>11</v>
+      </c>
+      <c r="M50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>moldtk2rc4tbj5t0</v>
-      </c>
-      <c r="C51" t="str">
-        <v>麦芽</v>
-      </c>
-      <c r="D51" t="str">
-        <v>MY</v>
-      </c>
-      <c r="E51" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F51" t="str">
-        <v>g</v>
+      <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2499,30 +2481,24 @@
         <v>11</v>
       </c>
       <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>11</v>
+      </c>
+      <c r="M51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>moldtk2qlts7jg2o</v>
-      </c>
-      <c r="C52" t="str">
-        <v>纳豆</v>
-      </c>
-      <c r="D52" t="str">
-        <v>NE</v>
-      </c>
-      <c r="E52" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F52" t="str">
-        <v>g</v>
+      <c r="C52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2540,30 +2516,24 @@
         <v>2</v>
       </c>
       <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>11</v>
+      </c>
+      <c r="M52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>moldtk2qlxqnh6r3</v>
-      </c>
-      <c r="C53" t="str">
-        <v>肉豆蔻</v>
-      </c>
-      <c r="D53" t="str">
-        <v>PEV</v>
-      </c>
-      <c r="E53" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F53" t="str">
-        <v>g</v>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2572,7 +2542,7 @@
         <v>8.1</v>
       </c>
       <c r="I53">
-        <v>35.2</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="J53">
         <v>43.3</v>
@@ -2581,30 +2551,24 @@
         <v>26</v>
       </c>
       <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>11</v>
+      </c>
+      <c r="M53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>moldtk2qwz6rpk3b</v>
-      </c>
-      <c r="C54" t="str">
-        <v>肉桂</v>
-      </c>
-      <c r="D54" t="str">
-        <v>PO</v>
-      </c>
-      <c r="E54" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F54" t="str">
-        <v>g</v>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2622,30 +2586,24 @@
         <v>15</v>
       </c>
       <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>11</v>
+      </c>
+      <c r="M54" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>moldtk2rlf84guip</v>
-      </c>
-      <c r="C55" t="str">
-        <v>重瓣红玫瑰</v>
-      </c>
-      <c r="D55" t="str">
-        <v>PXWX</v>
-      </c>
-      <c r="E55" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F55" t="str">
-        <v>g</v>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2663,30 +2621,24 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>11</v>
+      </c>
+      <c r="M55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>moldtk2rieryia5v</v>
-      </c>
-      <c r="C56" t="str">
-        <v>重瓣玫瑰花</v>
-      </c>
-      <c r="D56" t="str">
-        <v>PXXM</v>
-      </c>
-      <c r="E56" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F56" t="str">
-        <v>g</v>
+      <c r="C56" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2706,69 +2658,57 @@
       <c r="L56">
         <v>70</v>
       </c>
-      <c r="M56" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="M56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>moldtk2qpsf4flkb</v>
-      </c>
-      <c r="C57" t="str">
-        <v>芡实</v>
-      </c>
-      <c r="D57" t="str">
-        <v>QS</v>
-      </c>
-      <c r="E57" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F57" t="str">
-        <v>g</v>
+      <c r="C57" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I57">
         <v>0.3</v>
       </c>
       <c r="J57">
-        <v>79.6</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="K57">
         <v>28</v>
       </c>
       <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>11</v>
+      </c>
+      <c r="M57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>moldtk2o9cmxggha</v>
-      </c>
-      <c r="C58" t="str">
-        <v>白芷</v>
-      </c>
-      <c r="D58" t="str">
-        <v>RB</v>
-      </c>
-      <c r="E58" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F58" t="str">
-        <v>g</v>
+      <c r="C58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2780,7 +2720,7 @@
         <v>1.5</v>
       </c>
       <c r="J58">
-        <v>74.1</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="K58">
         <v>27</v>
@@ -2788,28 +2728,22 @@
       <c r="L58">
         <v>75</v>
       </c>
-      <c r="M58" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="M58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>moldtk2ox3slvz1z</v>
-      </c>
-      <c r="C59" t="str">
-        <v>草果</v>
-      </c>
-      <c r="D59" t="str">
-        <v>RE</v>
-      </c>
-      <c r="E59" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F59" t="str">
-        <v>g</v>
+      <c r="C59" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s">
+        <v>15</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2827,30 +2761,24 @@
         <v>5</v>
       </c>
       <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>11</v>
+      </c>
+      <c r="M59" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>moldtk2q4q1kwjtd</v>
-      </c>
-      <c r="C60" t="str">
-        <v>铁皮石斛</v>
-      </c>
-      <c r="D60" t="str">
-        <v>ROBL</v>
-      </c>
-      <c r="E60" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F60" t="str">
-        <v>g</v>
+      <c r="C60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2868,30 +2796,24 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>11</v>
+      </c>
+      <c r="M60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>moldtk2rs4ecbgek</v>
-      </c>
-      <c r="C61" t="str">
-        <v>显脉旋覆花</v>
-      </c>
-      <c r="D61" t="str">
-        <v>SNHC</v>
-      </c>
-      <c r="E61" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F61" t="str">
-        <v>g</v>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2909,30 +2831,24 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>11</v>
+      </c>
+      <c r="M61" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>moldtk2rhq7h56tr</v>
-      </c>
-      <c r="C62" t="str">
-        <v>桑葫鲜果</v>
-      </c>
-      <c r="D62" t="str">
-        <v>SSXG</v>
-      </c>
-      <c r="E62" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F62" t="str">
-        <v>g</v>
+      <c r="C62" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2950,30 +2866,24 @@
         <v>45</v>
       </c>
       <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="63">
+        <v>11</v>
+      </c>
+      <c r="M62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>moldtk2qxkjk6bdv</v>
-      </c>
-      <c r="C63" t="str">
-        <v>山药</v>
-      </c>
-      <c r="D63" t="str">
-        <v>SY</v>
-      </c>
-      <c r="E63" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F63" t="str">
-        <v>g</v>
+      <c r="C63" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -2993,28 +2903,22 @@
       <c r="L63">
         <v>48</v>
       </c>
-      <c r="M63" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="M63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>moldtk2r8w8hjcsv</v>
-      </c>
-      <c r="C64" t="str">
-        <v>山楂</v>
-      </c>
-      <c r="D64" t="str">
-        <v>SZ</v>
-      </c>
-      <c r="E64" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F64" t="str">
-        <v>g</v>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>15</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3034,28 +2938,22 @@
       <c r="L64">
         <v>70</v>
       </c>
-      <c r="M64" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="M64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>moldtk2seqan18jg</v>
-      </c>
-      <c r="C65" t="str">
-        <v>酸枣蜜炼</v>
-      </c>
-      <c r="D65" t="str">
-        <v>SZML</v>
-      </c>
-      <c r="E65" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F65" t="str">
-        <v>g</v>
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3073,30 +2971,24 @@
         <v>15</v>
       </c>
       <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>11</v>
+      </c>
+      <c r="M65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>moldtk2qe1v0xfkc</v>
-      </c>
-      <c r="C66" t="str">
-        <v>酸枣仁</v>
-      </c>
-      <c r="D66" t="str">
-        <v>SZR</v>
-      </c>
-      <c r="E66" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F66" t="str">
-        <v>g</v>
+      <c r="C66" t="s">
+        <v>81</v>
+      </c>
+      <c r="E66" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3116,28 +3008,22 @@
       <c r="L66">
         <v>380</v>
       </c>
-      <c r="M66" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="M66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>moldtk2qcofb482x</v>
-      </c>
-      <c r="C67" t="str">
-        <v>桃仁</v>
-      </c>
-      <c r="D67" t="str">
-        <v>TR</v>
-      </c>
-      <c r="E67" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F67" t="str">
-        <v>g</v>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3149,36 +3035,30 @@
         <v>0.8</v>
       </c>
       <c r="J67">
-        <v>77.9</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="K67">
         <v>3.8</v>
       </c>
       <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>11</v>
+      </c>
+      <c r="M67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>moldtk2pu4201yep</v>
-      </c>
-      <c r="C68" t="str">
-        <v>大枣</v>
-      </c>
-      <c r="D68" t="str">
-        <v>VL</v>
-      </c>
-      <c r="E68" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F68" t="str">
-        <v>g</v>
+      <c r="C68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s">
+        <v>15</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -3198,28 +3078,22 @@
       <c r="L68">
         <v>70</v>
       </c>
-      <c r="M68" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="M68" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>moldtk2pfpfbg7r0</v>
-      </c>
-      <c r="C69" t="str">
-        <v>短梗五加</v>
-      </c>
-      <c r="D69" t="str">
-        <v>VVSO</v>
-      </c>
-      <c r="E69" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F69" t="str">
-        <v>g</v>
+      <c r="C69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>15</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -3237,30 +3111,24 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>11</v>
+      </c>
+      <c r="M69" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>moldtk2rk1jvhpce</v>
-      </c>
-      <c r="C70" t="str">
-        <v>西红花</v>
-      </c>
-      <c r="D70" t="str">
-        <v>VWV</v>
-      </c>
-      <c r="E70" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F70" t="str">
-        <v>g</v>
+      <c r="C70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3272,36 +3140,30 @@
         <v>5.9</v>
       </c>
       <c r="J70">
-        <v>65.4</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>11</v>
+      </c>
+      <c r="M70" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>moldtk2pyi9z6d6u</v>
-      </c>
-      <c r="C71" t="str">
-        <v>低聚异麦芽糖</v>
-      </c>
-      <c r="D71" t="str">
-        <v>WUMC</v>
-      </c>
-      <c r="E71" t="str">
-        <v>辅料</v>
-      </c>
-      <c r="F71" t="str">
-        <v>g</v>
+      <c r="C71" t="s">
+        <v>86</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s">
+        <v>15</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3321,28 +3183,22 @@
       <c r="L71">
         <v>10.8</v>
       </c>
-      <c r="M71" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="M71" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>moldtk2r49dh0im3</v>
-      </c>
-      <c r="C72" t="str">
-        <v>杏仁</v>
-      </c>
-      <c r="D72" t="str">
-        <v>XR</v>
-      </c>
-      <c r="E72" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F72" t="str">
-        <v>g</v>
+      <c r="C72" t="s">
+        <v>87</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3360,30 +3216,24 @@
         <v>8</v>
       </c>
       <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>11</v>
+      </c>
+      <c r="M72" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="str">
-        <v>moldtk2qh3w1ruhg</v>
-      </c>
-      <c r="C73" t="str">
-        <v>乌梅</v>
-      </c>
-      <c r="D73" t="str">
-        <v>YD</v>
-      </c>
-      <c r="E73" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F73" t="str">
-        <v>g</v>
+      <c r="C73" t="s">
+        <v>88</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3392,10 +3242,10 @@
         <v>6.8</v>
       </c>
       <c r="I73">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J73">
-        <v>76.6</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="K73">
         <v>19</v>
@@ -3403,28 +3253,22 @@
       <c r="L73">
         <v>70</v>
       </c>
-      <c r="M73" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="M73" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="str">
-        <v>moldtk2rwyl0dtvl</v>
-      </c>
-      <c r="C74" t="str">
-        <v>鱼腥草</v>
-      </c>
-      <c r="D74" t="str">
-        <v>YXC</v>
-      </c>
-      <c r="E74" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F74" t="str">
-        <v>g</v>
+      <c r="C74" t="s">
+        <v>89</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>15</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -3442,30 +3286,24 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>11</v>
+      </c>
+      <c r="M74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="str">
-        <v>moldtk2rrn2kl553</v>
-      </c>
-      <c r="C75" t="str">
-        <v>薏苡仁</v>
-      </c>
-      <c r="D75" t="str">
-        <v>YYR</v>
-      </c>
-      <c r="E75" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F75" t="str">
-        <v>g</v>
+      <c r="C75" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" t="s">
+        <v>15</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3483,30 +3321,24 @@
         <v>15</v>
       </c>
       <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75" t="str">
-        <v>full_reimport</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>11</v>
+      </c>
+      <c r="M75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="str">
-        <v>moldtk2q1wcrv4zu</v>
-      </c>
-      <c r="C76" t="str">
-        <v>平卧菊三七</v>
-      </c>
-      <c r="D76" t="str">
-        <v>ZFQJ</v>
-      </c>
-      <c r="E76" t="str">
-        <v>药材</v>
-      </c>
-      <c r="F76" t="str">
-        <v>g</v>
+      <c r="C76" t="s">
+        <v>91</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" t="s">
+        <v>15</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3518,21 +3350,24 @@
         <v>3.9</v>
       </c>
       <c r="J76">
-        <v>67.6</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="K76">
         <v>17.5</v>
       </c>
       <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76" t="str">
-        <v>full_reimport</v>
+        <v>11</v>
+      </c>
+      <c r="M76" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M76"/>
+    <ignoredError sqref="A1:M1 A48:A76 A35:A47 E36:M36 A2:A34 E3:M3 E56:M56 C48:C76 C35:C47 C2:C34 E2:K2 M2 E6:M6 E4:K4 M4 E5:K5 M5 E9:M9 E7:K7 M7 E8:K8 M8 E14:M16 E10:K10 M10 E11:K11 M11 E12:K12 M12 E13:K13 M13 E18:M18 E17:K17 M17 E21:M21 E19:K19 M19 E20:K20 M20 E23:M24 E22:K22 M22 E30:M30 E25:K25 M25 E26:K26 M26 E27:K27 M27 E28:K28 M28 E29:K29 M29 E34:K34 E31:K31 M31 E32:K32 M32 E33:K33 M33 M34 E35:K35 M35 E40:M40 E37:K37 M37 E38:K38 M38 E39:K39 M39 E46:M46 E41:K41 M41 E42:K42 M42 E43:K43 M43 E44:K44 M44 E45:K45 M45 E47:K47 M47 E48:K48 M48 E49:K49 M49 E50:K50 M50 E51:K51 M51 E52:K52 M52 E53:K53 M53 E54:K54 M54 E55:K55 M55 E58:M58 E57:K57 M57 E63:M64 E59:K59 M59 E60:K60 M60 E61:K61 M61 E62:K62 M62 E66:M66 E65:K65 M65 E68:M68 E67:K67 M67 E71:M71 E69:K69 M69 E70:K70 M70 E73:M73 E72:K72 M72 E76:K76 E74:K74 M74 E75:K75 M75 M76" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test/原料数据库导入_完整版_已清理.xlsx
+++ b/test/原料数据库导入_完整版_已清理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProgramData\workspace-codeby\ting-studio\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088544DD-8F8B-48A8-962E-AD53701FE1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2DA324-F338-4AEF-BC5B-EA6060F3D72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="93">
   <si>
     <t>序号</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>平卧菊三七</t>
+  </si>
+  <si>
+    <t>竹叶黄酮</t>
   </si>
 </sst>
 </file>
@@ -679,8 +682,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M76"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:M77"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
     <col min="2" max="2" width="18.875" customWidth="1"/>
@@ -696,7 +699,7 @@
     <col min="13" max="13" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -772,7 +775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -807,7 +810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -842,7 +845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -877,7 +880,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -912,7 +915,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -947,7 +950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -982,7 +985,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1087,7 +1090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1122,7 +1125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1157,7 +1160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1227,7 +1230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1297,7 +1300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1332,7 +1335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1367,7 +1370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1507,7 +1510,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1542,7 +1545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1577,7 +1580,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1612,7 +1615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1647,7 +1650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1717,7 +1720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1752,7 +1755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1822,7 +1825,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1857,7 +1860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1892,7 +1895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1927,7 +1930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1997,7 +2000,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2067,7 +2070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2102,7 +2105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2137,7 +2140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2172,7 +2175,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2242,7 +2245,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2277,7 +2280,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2312,7 +2315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2347,7 +2350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2382,7 +2385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2417,7 +2420,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2452,7 +2455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2487,7 +2490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2522,7 +2525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2557,7 +2560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2592,7 +2595,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2627,7 +2630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2662,7 +2665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2732,7 +2735,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2767,7 +2770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2802,7 +2805,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2837,7 +2840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2872,7 +2875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3082,7 +3085,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3117,7 +3120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3152,7 +3155,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3187,7 +3190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3222,7 +3225,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3257,7 +3260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3292,7 +3295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3327,7 +3330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3359,6 +3362,41 @@
         <v>11</v>
       </c>
       <c r="M76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="C77" t="s">
+        <v>92</v>
+      </c>
+      <c r="E77" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>11</v>
+      </c>
+      <c r="M77" t="s">
         <v>16</v>
       </c>
     </row>
